--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B65D5EE-DCAE-4F5B-81B2-E7B970792EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BE2BEF-BB97-4C07-8D3D-522ABF4EAC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -249,7 +249,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="33">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -309,17 +309,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -431,19 +420,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -600,31 +576,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -635,26 +600,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -664,72 +622,66 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -739,95 +691,38 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -835,41 +730,111 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,7 +859,7 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>23920</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>81493</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1804131" cy="1576024"/>
@@ -932,7 +897,7 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>152401</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>67733</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1205130" cy="607695"/>
@@ -1170,7 +1135,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL996"/>
+  <dimension ref="A1:AL997"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.28515625" style="7" customWidth="1"/>
@@ -1231,1009 +1196,1004 @@
       <c r="AK1" s="8"/>
       <c r="AL1" s="8"/>
     </row>
-    <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="30" t="s">
+    <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="8"/>
+      <c r="B2" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="40" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="86" t="s">
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="87"/>
-      <c r="U2" s="87"/>
-      <c r="V2" s="87"/>
-      <c r="W2" s="87"/>
-      <c r="X2" s="87"/>
-      <c r="Y2" s="87"/>
-      <c r="Z2" s="87"/>
-      <c r="AA2" s="87"/>
-      <c r="AB2" s="88"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="75" t="s">
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="77"/>
+      <c r="Z2" s="77"/>
+      <c r="AA2" s="77"/>
+      <c r="AB2" s="78"/>
+      <c r="AC2" s="88"/>
+      <c r="AD2" s="89"/>
+      <c r="AE2" s="89"/>
+      <c r="AF2" s="89"/>
+      <c r="AG2" s="89"/>
+      <c r="AH2" s="89"/>
+      <c r="AI2" s="89"/>
+      <c r="AJ2" s="89"/>
+      <c r="AK2" s="89"/>
+      <c r="AL2" s="90"/>
+    </row>
+    <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="66"/>
+      <c r="R3" s="67"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
+      <c r="Z3" s="82"/>
+      <c r="AA3" s="82"/>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="AE2" s="75"/>
-      <c r="AF2" s="75"/>
-      <c r="AG2" s="75"/>
-      <c r="AH2" s="75"/>
-      <c r="AI2" s="75"/>
-      <c r="AJ2" s="75"/>
-      <c r="AK2" s="10"/>
-      <c r="AL2" s="11"/>
-    </row>
-    <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="89"/>
-      <c r="T3" s="90"/>
-      <c r="U3" s="90"/>
-      <c r="V3" s="90"/>
-      <c r="W3" s="90"/>
-      <c r="X3" s="90"/>
-      <c r="Y3" s="90"/>
-      <c r="Z3" s="90"/>
-      <c r="AA3" s="90"/>
-      <c r="AB3" s="91"/>
-      <c r="AC3" s="12"/>
-      <c r="AD3" s="76"/>
-      <c r="AE3" s="76"/>
-      <c r="AF3" s="76"/>
-      <c r="AG3" s="76"/>
-      <c r="AH3" s="76"/>
-      <c r="AI3" s="76"/>
-      <c r="AJ3" s="76"/>
-      <c r="AK3" s="13"/>
-      <c r="AL3" s="14"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="86"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="34"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="85"/>
-      <c r="O4" s="39" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="68"/>
+      <c r="P4" s="69"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="81"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="72"/>
+      <c r="AE4" s="72"/>
+      <c r="AF4" s="72"/>
+      <c r="AG4" s="72"/>
+      <c r="AH4" s="72"/>
+      <c r="AI4" s="72"/>
+      <c r="AJ4" s="72"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="11"/>
+    </row>
+    <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="66"/>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="40"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="86" t="s">
+      <c r="P5" s="63"/>
+      <c r="Q5" s="63"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="87"/>
-      <c r="U4" s="87"/>
-      <c r="V4" s="87"/>
-      <c r="W4" s="87"/>
-      <c r="X4" s="87"/>
-      <c r="Y4" s="87"/>
-      <c r="Z4" s="87"/>
-      <c r="AA4" s="87"/>
-      <c r="AB4" s="88"/>
-      <c r="AC4" s="15"/>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="76"/>
-      <c r="AF4" s="76"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="76"/>
-      <c r="AK4" s="16"/>
-      <c r="AL4" s="17"/>
-    </row>
-    <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="92" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="93"/>
-      <c r="M5" s="93"/>
-      <c r="N5" s="94"/>
-      <c r="O5" s="42"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="89"/>
-      <c r="T5" s="90"/>
-      <c r="U5" s="90"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="90"/>
-      <c r="X5" s="90"/>
-      <c r="Y5" s="90"/>
-      <c r="Z5" s="90"/>
-      <c r="AA5" s="90"/>
-      <c r="AB5" s="91"/>
-      <c r="AC5" s="15"/>
-      <c r="AD5" s="76"/>
-      <c r="AE5" s="76"/>
-      <c r="AF5" s="76"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="76"/>
-      <c r="AI5" s="76"/>
-      <c r="AJ5" s="76"/>
-      <c r="AK5" s="16"/>
-      <c r="AL5" s="18"/>
-    </row>
-    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T5" s="77"/>
+      <c r="U5" s="77"/>
+      <c r="V5" s="77"/>
+      <c r="W5" s="77"/>
+      <c r="X5" s="77"/>
+      <c r="Y5" s="77"/>
+      <c r="Z5" s="77"/>
+      <c r="AA5" s="77"/>
+      <c r="AB5" s="78"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="72"/>
+      <c r="AE5" s="72"/>
+      <c r="AF5" s="72"/>
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="72"/>
+      <c r="AI5" s="72"/>
+      <c r="AJ5" s="72"/>
+      <c r="AK5" s="13"/>
+      <c r="AL5" s="14"/>
+    </row>
+    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="65"/>
+      <c r="P6" s="66"/>
+      <c r="Q6" s="66"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
+      <c r="Y6" s="80"/>
+      <c r="Z6" s="80"/>
+      <c r="AA6" s="80"/>
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="72"/>
+      <c r="AE6" s="72"/>
+      <c r="AF6" s="72"/>
+      <c r="AG6" s="72"/>
+      <c r="AH6" s="72"/>
+      <c r="AI6" s="72"/>
+      <c r="AJ6" s="72"/>
+      <c r="AK6" s="13"/>
+      <c r="AL6" s="15"/>
+    </row>
+    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="71" t="s">
+      <c r="C7" s="92"/>
+      <c r="D7" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="64" t="s">
+      <c r="E7" s="71"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="71"/>
+      <c r="I7" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="64"/>
-      <c r="K6" s="74" t="s">
+      <c r="J7" s="93"/>
+      <c r="K7" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
-      <c r="N6" s="74"/>
-      <c r="O6" s="39" t="s">
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="95"/>
+      <c r="O7" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="41"/>
-      <c r="S6" s="87" t="s">
+      <c r="P7" s="63"/>
+      <c r="Q7" s="63"/>
+      <c r="R7" s="64"/>
+      <c r="S7" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="87"/>
-      <c r="U6" s="87"/>
-      <c r="V6" s="87"/>
-      <c r="W6" s="87"/>
-      <c r="X6" s="87"/>
-      <c r="Y6" s="87"/>
-      <c r="Z6" s="87"/>
-      <c r="AA6" s="87"/>
-      <c r="AB6" s="88"/>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="76"/>
-      <c r="AE6" s="76"/>
-      <c r="AF6" s="76"/>
-      <c r="AG6" s="76"/>
-      <c r="AH6" s="76"/>
-      <c r="AI6" s="76"/>
-      <c r="AJ6" s="76"/>
-      <c r="AK6" s="16"/>
-      <c r="AL6" s="18"/>
-    </row>
-    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="30" t="s">
+      <c r="T7" s="77"/>
+      <c r="U7" s="77"/>
+      <c r="V7" s="77"/>
+      <c r="W7" s="77"/>
+      <c r="X7" s="77"/>
+      <c r="Y7" s="77"/>
+      <c r="Z7" s="77"/>
+      <c r="AA7" s="77"/>
+      <c r="AB7" s="78"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="72"/>
+      <c r="AE7" s="72"/>
+      <c r="AF7" s="72"/>
+      <c r="AG7" s="72"/>
+      <c r="AH7" s="72"/>
+      <c r="AI7" s="72"/>
+      <c r="AJ7" s="72"/>
+      <c r="AK7" s="13"/>
+      <c r="AL7" s="15"/>
+    </row>
+    <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
-      <c r="O7" s="42"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="95"/>
-      <c r="T7" s="95"/>
-      <c r="U7" s="95"/>
-      <c r="V7" s="95"/>
-      <c r="W7" s="95"/>
-      <c r="X7" s="95"/>
-      <c r="Y7" s="95"/>
-      <c r="Z7" s="95"/>
-      <c r="AA7" s="95"/>
-      <c r="AB7" s="96"/>
-      <c r="AC7" s="15"/>
-      <c r="AD7" s="76"/>
-      <c r="AE7" s="76"/>
-      <c r="AF7" s="76"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="76"/>
-      <c r="AI7" s="76"/>
-      <c r="AJ7" s="76"/>
-      <c r="AK7" s="16"/>
-      <c r="AL7" s="18"/>
-    </row>
-    <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="95"/>
-      <c r="T8" s="95"/>
-      <c r="U8" s="95"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="95"/>
-      <c r="X8" s="95"/>
-      <c r="Y8" s="95"/>
-      <c r="Z8" s="95"/>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="15"/>
-      <c r="AD8" s="76"/>
-      <c r="AE8" s="76"/>
-      <c r="AF8" s="76"/>
-      <c r="AG8" s="76"/>
-      <c r="AH8" s="76"/>
-      <c r="AI8" s="76"/>
-      <c r="AJ8" s="76"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="18"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="74"/>
+      <c r="O8" s="66"/>
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="82"/>
+      <c r="T8" s="82"/>
+      <c r="U8" s="82"/>
+      <c r="V8" s="82"/>
+      <c r="W8" s="82"/>
+      <c r="X8" s="82"/>
+      <c r="Y8" s="82"/>
+      <c r="Z8" s="82"/>
+      <c r="AA8" s="82"/>
+      <c r="AB8" s="83"/>
+      <c r="AC8" s="12"/>
+      <c r="AD8" s="72"/>
+      <c r="AE8" s="72"/>
+      <c r="AF8" s="72"/>
+      <c r="AG8" s="72"/>
+      <c r="AH8" s="72"/>
+      <c r="AI8" s="72"/>
+      <c r="AJ8" s="72"/>
+      <c r="AK8" s="13"/>
+      <c r="AL8" s="15"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="95"/>
-      <c r="T9" s="95"/>
-      <c r="U9" s="95"/>
-      <c r="V9" s="95"/>
-      <c r="W9" s="95"/>
-      <c r="X9" s="95"/>
-      <c r="Y9" s="95"/>
-      <c r="Z9" s="95"/>
-      <c r="AA9" s="95"/>
-      <c r="AB9" s="96"/>
-      <c r="AC9" s="15"/>
-      <c r="AD9" s="76"/>
-      <c r="AE9" s="76"/>
-      <c r="AF9" s="76"/>
-      <c r="AG9" s="76"/>
-      <c r="AH9" s="76"/>
-      <c r="AI9" s="76"/>
-      <c r="AJ9" s="76"/>
-      <c r="AK9" s="16"/>
-      <c r="AL9" s="18"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="74"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="66"/>
+      <c r="Q9" s="66"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="82"/>
+      <c r="T9" s="82"/>
+      <c r="U9" s="82"/>
+      <c r="V9" s="82"/>
+      <c r="W9" s="82"/>
+      <c r="X9" s="82"/>
+      <c r="Y9" s="82"/>
+      <c r="Z9" s="82"/>
+      <c r="AA9" s="82"/>
+      <c r="AB9" s="83"/>
+      <c r="AC9" s="12"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="72"/>
+      <c r="AF9" s="72"/>
+      <c r="AG9" s="72"/>
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="72"/>
+      <c r="AJ9" s="72"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="15"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="55"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="74"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="82"/>
+      <c r="T10" s="82"/>
+      <c r="U10" s="82"/>
+      <c r="V10" s="82"/>
+      <c r="W10" s="82"/>
+      <c r="X10" s="82"/>
+      <c r="Y10" s="82"/>
+      <c r="Z10" s="82"/>
+      <c r="AA10" s="82"/>
+      <c r="AB10" s="83"/>
+      <c r="AC10" s="12"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="13"/>
+      <c r="AL10" s="15"/>
+    </row>
+    <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="73"/>
-      <c r="N10" s="73"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="46"/>
-      <c r="Q10" s="46"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="90"/>
-      <c r="T10" s="90"/>
-      <c r="U10" s="90"/>
-      <c r="V10" s="90"/>
-      <c r="W10" s="90"/>
-      <c r="X10" s="90"/>
-      <c r="Y10" s="90"/>
-      <c r="Z10" s="90"/>
-      <c r="AA10" s="90"/>
-      <c r="AB10" s="91"/>
-      <c r="AC10" s="36" t="s">
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="97"/>
+      <c r="I11" s="97"/>
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="97"/>
+      <c r="N11" s="98"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="80"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="38"/>
-    </row>
-    <row r="11" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
-      <c r="AJ11" s="1"/>
-      <c r="AK11" s="1"/>
-      <c r="AL11" s="1"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
+      <c r="AF11" s="60"/>
+      <c r="AG11" s="60"/>
+      <c r="AH11" s="60"/>
+      <c r="AI11" s="60"/>
+      <c r="AJ11" s="60"/>
+      <c r="AK11" s="60"/>
+      <c r="AL11" s="61"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
-      <c r="B12" s="54" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="1"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="1"/>
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+    </row>
+    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
+      <c r="B13" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="54"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="54"/>
-      <c r="AC12" s="54"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-    </row>
-    <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="54"/>
-      <c r="F13" s="54"/>
-      <c r="G13" s="54"/>
-      <c r="H13" s="54"/>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="54"/>
-      <c r="X13" s="54"/>
-      <c r="Y13" s="54"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="54"/>
-      <c r="AC13" s="54"/>
-      <c r="AD13" s="54"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="54"/>
-      <c r="AH13" s="54"/>
-      <c r="AI13" s="54"/>
-      <c r="AJ13" s="54"/>
-      <c r="AK13" s="54"/>
-      <c r="AL13" s="54"/>
-    </row>
-    <row r="14" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="47"/>
+      <c r="X13" s="47"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
+      <c r="AA13" s="47"/>
+      <c r="AB13" s="47"/>
+      <c r="AC13" s="47"/>
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="47"/>
+      <c r="AF13" s="47"/>
+      <c r="AG13" s="47"/>
+      <c r="AH13" s="47"/>
+      <c r="AI13" s="47"/>
+      <c r="AJ13" s="47"/>
+      <c r="AK13" s="47"/>
+      <c r="AL13" s="47"/>
+    </row>
+    <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="68"/>
-      <c r="P14" s="68"/>
-      <c r="Q14" s="68"/>
-      <c r="R14" s="68"/>
-      <c r="S14" s="68"/>
-      <c r="T14" s="68"/>
-      <c r="U14" s="68"/>
-      <c r="V14" s="68"/>
-      <c r="W14" s="68"/>
-      <c r="X14" s="68"/>
-      <c r="Y14" s="68"/>
-      <c r="Z14" s="68"/>
-      <c r="AA14" s="68"/>
-      <c r="AB14" s="68"/>
-      <c r="AC14" s="68"/>
-      <c r="AD14" s="68"/>
-      <c r="AE14" s="68"/>
-      <c r="AF14" s="68"/>
-      <c r="AG14" s="68"/>
-      <c r="AH14" s="68"/>
-      <c r="AI14" s="68"/>
-      <c r="AJ14" s="68"/>
-      <c r="AK14" s="68"/>
-      <c r="AL14" s="68"/>
-    </row>
-    <row r="15" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+      <c r="W14" s="47"/>
+      <c r="X14" s="47"/>
+      <c r="Y14" s="47"/>
+      <c r="Z14" s="47"/>
+      <c r="AA14" s="47"/>
+      <c r="AB14" s="47"/>
+      <c r="AC14" s="47"/>
+      <c r="AD14" s="47"/>
+      <c r="AE14" s="47"/>
+      <c r="AF14" s="47"/>
+      <c r="AG14" s="47"/>
+      <c r="AH14" s="47"/>
+      <c r="AI14" s="47"/>
+      <c r="AJ14" s="47"/>
+      <c r="AK14" s="47"/>
+      <c r="AL14" s="47"/>
+    </row>
+    <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
-      <c r="AJ15" s="1"/>
-      <c r="AK15" s="1"/>
-      <c r="AL15" s="1"/>
-    </row>
-    <row r="16" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="28" t="s">
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="38"/>
+      <c r="AL15" s="38"/>
+    </row>
+    <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="1"/>
+      <c r="AD16" s="1"/>
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+    </row>
+    <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+      <c r="B17" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="57" t="s">
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-      <c r="J16" s="57"/>
-      <c r="K16" s="57"/>
-      <c r="L16" s="57"/>
-      <c r="M16" s="57"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="57"/>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="57"/>
-      <c r="R16" s="57"/>
-      <c r="S16" s="57"/>
-      <c r="T16" s="57"/>
-      <c r="U16" s="57"/>
-      <c r="V16" s="57"/>
-      <c r="W16" s="57"/>
-      <c r="X16" s="57"/>
-      <c r="Y16" s="57"/>
-      <c r="Z16" s="57"/>
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="57"/>
-      <c r="AC16" s="57"/>
-      <c r="AD16" s="57"/>
-      <c r="AE16" s="57"/>
-      <c r="AF16" s="57"/>
-      <c r="AG16" s="57"/>
-      <c r="AH16" s="57"/>
-      <c r="AI16" s="57"/>
-      <c r="AJ16" s="57"/>
-      <c r="AK16" s="57"/>
-      <c r="AL16" s="57"/>
-    </row>
-    <row r="17" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
-      <c r="AI17" s="1"/>
-      <c r="AJ17" s="1"/>
-      <c r="AK17" s="1"/>
-      <c r="AL17" s="1"/>
-    </row>
-    <row r="18" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="28" t="s">
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="48"/>
+      <c r="X17" s="48"/>
+      <c r="Y17" s="48"/>
+      <c r="Z17" s="48"/>
+      <c r="AA17" s="48"/>
+      <c r="AB17" s="48"/>
+      <c r="AC17" s="48"/>
+      <c r="AD17" s="48"/>
+      <c r="AE17" s="48"/>
+      <c r="AF17" s="48"/>
+      <c r="AG17" s="48"/>
+      <c r="AH17" s="48"/>
+      <c r="AI17" s="48"/>
+      <c r="AJ17" s="48"/>
+      <c r="AK17" s="48"/>
+      <c r="AL17" s="48"/>
+    </row>
+    <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="1"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+    </row>
+    <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3"/>
+      <c r="B19" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="57" t="s">
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
-      <c r="K18" s="57"/>
-      <c r="L18" s="57"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="57"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="57"/>
-      <c r="R18" s="57"/>
-      <c r="S18" s="57"/>
-      <c r="T18" s="57"/>
-      <c r="U18" s="57"/>
-      <c r="V18" s="57"/>
-      <c r="W18" s="57"/>
-      <c r="X18" s="57"/>
-      <c r="Y18" s="57"/>
-      <c r="Z18" s="57"/>
-      <c r="AA18" s="57"/>
-      <c r="AB18" s="57"/>
-      <c r="AC18" s="57"/>
-      <c r="AD18" s="57"/>
-      <c r="AE18" s="57"/>
-      <c r="AF18" s="57"/>
-      <c r="AG18" s="57"/>
-      <c r="AH18" s="57"/>
-      <c r="AI18" s="57"/>
-      <c r="AJ18" s="57"/>
-      <c r="AK18" s="57"/>
-      <c r="AL18" s="57"/>
-    </row>
-    <row r="19" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="1"/>
-      <c r="AI19" s="1"/>
-      <c r="AJ19" s="1"/>
-      <c r="AK19" s="1"/>
-      <c r="AL19" s="1"/>
-    </row>
-    <row r="20" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="48"/>
+      <c r="X19" s="48"/>
+      <c r="Y19" s="48"/>
+      <c r="Z19" s="48"/>
+      <c r="AA19" s="48"/>
+      <c r="AB19" s="48"/>
+      <c r="AC19" s="48"/>
+      <c r="AD19" s="48"/>
+      <c r="AE19" s="48"/>
+      <c r="AF19" s="48"/>
+      <c r="AG19" s="48"/>
+      <c r="AH19" s="48"/>
+      <c r="AI19" s="48"/>
+      <c r="AJ19" s="48"/>
+      <c r="AK19" s="48"/>
+      <c r="AL19" s="48"/>
+    </row>
+    <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+    </row>
+    <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
+      <c r="B21" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="26" t="s">
+      <c r="C21" s="25"/>
+      <c r="D21" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="26" t="s">
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="26" t="s">
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="80" t="s">
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="81"/>
-      <c r="AC20" s="81"/>
-      <c r="AD20" s="81"/>
-      <c r="AE20" s="82"/>
-      <c r="AF20" s="65" t="s">
+      <c r="AA21" s="27"/>
+      <c r="AB21" s="27"/>
+      <c r="AC21" s="27"/>
+      <c r="AD21" s="27"/>
+      <c r="AE21" s="28"/>
+      <c r="AF21" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="27"/>
-      <c r="AI20" s="27"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="66"/>
-      <c r="AL20" s="1"/>
-    </row>
-    <row r="21" spans="1:38" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="52">
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="25"/>
+      <c r="AI21" s="25"/>
+      <c r="AJ21" s="25"/>
+      <c r="AK21" s="36"/>
+      <c r="AL21" s="1"/>
+    </row>
+    <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="21">
         <v>1</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="62" t="s">
+      <c r="C22" s="22"/>
+      <c r="D22" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="63">
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="32">
         <v>1</v>
       </c>
-      <c r="T21" s="53"/>
-      <c r="U21" s="53"/>
-      <c r="V21" s="53"/>
-      <c r="W21" s="69" t="s">
+      <c r="T22" s="22"/>
+      <c r="U22" s="22"/>
+      <c r="V22" s="22"/>
+      <c r="W22" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="53"/>
-      <c r="Z21" s="48" t="s">
+      <c r="X22" s="22"/>
+      <c r="Y22" s="22"/>
+      <c r="Z22" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49"/>
-      <c r="AE21" s="50"/>
-      <c r="AF21" s="55" t="e">
-        <f>S21*Z21</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AG21" s="53"/>
-      <c r="AH21" s="53"/>
-      <c r="AI21" s="53"/>
-      <c r="AJ21" s="53"/>
-      <c r="AK21" s="56"/>
-      <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="52">
-        <v>2</v>
-      </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
-      <c r="I22" s="53"/>
-      <c r="J22" s="53"/>
-      <c r="K22" s="53"/>
-      <c r="L22" s="53"/>
-      <c r="M22" s="53"/>
-      <c r="N22" s="53"/>
-      <c r="O22" s="53"/>
-      <c r="P22" s="53"/>
-      <c r="Q22" s="53"/>
-      <c r="R22" s="53"/>
-      <c r="S22" s="63">
-        <v>1</v>
-      </c>
-      <c r="T22" s="53"/>
-      <c r="U22" s="53"/>
-      <c r="V22" s="53"/>
-      <c r="W22" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="X22" s="53"/>
-      <c r="Y22" s="53"/>
-      <c r="Z22" s="77" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA22" s="78"/>
-      <c r="AB22" s="78"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="79"/>
-      <c r="AF22" s="55" t="e">
+      <c r="AA22" s="44"/>
+      <c r="AB22" s="44"/>
+      <c r="AC22" s="44"/>
+      <c r="AD22" s="44"/>
+      <c r="AE22" s="45"/>
+      <c r="AF22" s="33" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="53"/>
-      <c r="AH22" s="53"/>
-      <c r="AI22" s="53"/>
-      <c r="AJ22" s="53"/>
-      <c r="AK22" s="56"/>
+      <c r="AG22" s="22"/>
+      <c r="AH22" s="22"/>
+      <c r="AI22" s="22"/>
+      <c r="AJ22" s="22"/>
+      <c r="AK22" s="34"/>
       <c r="AL22" s="3"/>
     </row>
-    <row r="23" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
-      <c r="AB23" s="4"/>
-      <c r="AC23" s="4"/>
-      <c r="AD23" s="4"/>
-      <c r="AE23" s="4"/>
-      <c r="AF23" s="4"/>
-      <c r="AG23" s="4"/>
-      <c r="AH23" s="4"/>
-      <c r="AI23" s="4"/>
-      <c r="AJ23" s="4"/>
-      <c r="AK23" s="4"/>
-      <c r="AL23" s="1"/>
-    </row>
-    <row r="24" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="5"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="5"/>
-      <c r="AD24" s="21"/>
-      <c r="AE24" s="21" t="s">
-        <v>27</v>
+    <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="21">
+        <v>2</v>
       </c>
-      <c r="AF24" s="61" t="e">
-        <f>SUM(AF21:AK22)</f>
+      <c r="C23" s="22"/>
+      <c r="D23" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
+      <c r="S23" s="32">
+        <v>1</v>
+      </c>
+      <c r="T23" s="22"/>
+      <c r="U23" s="22"/>
+      <c r="V23" s="22"/>
+      <c r="W23" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="X23" s="22"/>
+      <c r="Y23" s="22"/>
+      <c r="Z23" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA23" s="51"/>
+      <c r="AB23" s="51"/>
+      <c r="AC23" s="51"/>
+      <c r="AD23" s="51"/>
+      <c r="AE23" s="52"/>
+      <c r="AF23" s="33" t="e">
+        <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG24" s="29"/>
-      <c r="AH24" s="29"/>
-      <c r="AI24" s="29"/>
-      <c r="AJ24" s="29"/>
-      <c r="AK24" s="29"/>
+      <c r="AG23" s="22"/>
+      <c r="AH23" s="22"/>
+      <c r="AI23" s="22"/>
+      <c r="AJ23" s="22"/>
+      <c r="AK23" s="34"/>
+      <c r="AL23" s="3"/>
+    </row>
+    <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
       <c r="AL24" s="1"/>
     </row>
     <row r="25" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2266,18 +2226,19 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21" t="s">
-        <v>28</v>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16" t="s">
+        <v>27</v>
       </c>
-      <c r="AF25" s="61" t="s">
-        <v>29</v>
+      <c r="AF25" s="41" t="e">
+        <f>SUM(AF22:AK23)</f>
+        <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="29"/>
-      <c r="AH25" s="29"/>
-      <c r="AI25" s="29"/>
-      <c r="AJ25" s="29"/>
-      <c r="AK25" s="29"/>
+      <c r="AG25" s="42"/>
+      <c r="AH25" s="42"/>
+      <c r="AI25" s="42"/>
+      <c r="AJ25" s="42"/>
+      <c r="AK25" s="42"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2310,482 +2271,484 @@
       <c r="AA26" s="5"/>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
-      <c r="AD26" s="21"/>
-      <c r="AE26" s="21" t="s">
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF26" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="AG26" s="42"/>
+      <c r="AH26" s="42"/>
+      <c r="AI26" s="42"/>
+      <c r="AJ26" s="42"/>
+      <c r="AK26" s="42"/>
+      <c r="AL26" s="1"/>
+    </row>
+    <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+      <c r="W27" s="1"/>
+      <c r="X27" s="1"/>
+      <c r="Y27" s="1"/>
+      <c r="Z27" s="5"/>
+      <c r="AA27" s="5"/>
+      <c r="AB27" s="5"/>
+      <c r="AC27" s="5"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="AF26" s="61" t="e">
-        <f>SUM(AF24:AK25)</f>
+      <c r="AF27" s="41" t="e">
+        <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG26" s="29"/>
-      <c r="AH26" s="29"/>
-      <c r="AI26" s="29"/>
-      <c r="AJ26" s="29"/>
-      <c r="AK26" s="29"/>
-      <c r="AL26" s="1"/>
-    </row>
-    <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="67" t="s">
+      <c r="AG27" s="42"/>
+      <c r="AH27" s="42"/>
+      <c r="AI27" s="42"/>
+      <c r="AJ27" s="42"/>
+      <c r="AK27" s="42"/>
+      <c r="AL27" s="1"/>
+    </row>
+    <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="67"/>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="67"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
-      <c r="W27" s="67"/>
-      <c r="X27" s="67"/>
-      <c r="Y27" s="67"/>
-      <c r="Z27" s="67"/>
-      <c r="AA27" s="67"/>
-      <c r="AB27" s="67"/>
-      <c r="AC27" s="67"/>
-      <c r="AD27" s="67"/>
-      <c r="AE27" s="67"/>
-      <c r="AF27" s="67"/>
-      <c r="AG27" s="67"/>
-      <c r="AH27" s="67"/>
-      <c r="AI27" s="67"/>
-      <c r="AJ27" s="67"/>
-      <c r="AK27" s="67"/>
-      <c r="AL27" s="67"/>
-    </row>
-    <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="3"/>
-      <c r="B28" s="57" t="s">
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="37"/>
+      <c r="P28" s="37"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="37"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
+      <c r="AA28" s="37"/>
+      <c r="AB28" s="37"/>
+      <c r="AC28" s="37"/>
+      <c r="AD28" s="37"/>
+      <c r="AE28" s="37"/>
+      <c r="AF28" s="37"/>
+      <c r="AG28" s="37"/>
+      <c r="AH28" s="37"/>
+      <c r="AI28" s="37"/>
+      <c r="AJ28" s="37"/>
+      <c r="AK28" s="37"/>
+      <c r="AL28" s="37"/>
+    </row>
+    <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="57"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="57"/>
-      <c r="J28" s="57"/>
-      <c r="K28" s="57"/>
-      <c r="L28" s="57"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="57"/>
-      <c r="O28" s="57"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="57"/>
-      <c r="R28" s="57"/>
-      <c r="S28" s="57"/>
-      <c r="T28" s="57"/>
-      <c r="U28" s="57"/>
-      <c r="V28" s="57"/>
-      <c r="W28" s="57"/>
-      <c r="X28" s="57"/>
-      <c r="Y28" s="57"/>
-      <c r="Z28" s="57"/>
-      <c r="AA28" s="57"/>
-      <c r="AB28" s="57"/>
-      <c r="AC28" s="57"/>
-      <c r="AD28" s="57"/>
-      <c r="AE28" s="57"/>
-      <c r="AF28" s="57"/>
-      <c r="AG28" s="57"/>
-      <c r="AH28" s="57"/>
-      <c r="AI28" s="57"/>
-      <c r="AJ28" s="57"/>
-      <c r="AK28" s="3"/>
-      <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29" s="2"/>
-      <c r="V29" s="2"/>
-      <c r="W29" s="2"/>
-      <c r="X29" s="2"/>
-      <c r="Y29" s="2"/>
-      <c r="Z29" s="2"/>
-      <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-      <c r="AD29" s="2"/>
-      <c r="AE29" s="2"/>
-      <c r="AF29" s="2"/>
-      <c r="AG29" s="2"/>
-      <c r="AH29" s="2"/>
-      <c r="AI29" s="2"/>
-      <c r="AJ29" s="2"/>
-      <c r="AK29" s="2"/>
-      <c r="AL29" s="2"/>
-    </row>
-    <row r="30" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="48"/>
+      <c r="X29" s="48"/>
+      <c r="Y29" s="48"/>
+      <c r="Z29" s="48"/>
+      <c r="AA29" s="48"/>
+      <c r="AB29" s="48"/>
+      <c r="AC29" s="48"/>
+      <c r="AD29" s="48"/>
+      <c r="AE29" s="48"/>
+      <c r="AF29" s="48"/>
+      <c r="AG29" s="48"/>
+      <c r="AH29" s="48"/>
+      <c r="AI29" s="48"/>
+      <c r="AJ29" s="48"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+    </row>
+    <row r="30" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1"/>
-      <c r="AE30" s="1"/>
-      <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-      <c r="AH30" s="1"/>
-      <c r="AI30" s="1"/>
-      <c r="AJ30" s="1"/>
-      <c r="AK30" s="1"/>
-      <c r="AL30" s="1"/>
-    </row>
-    <row r="31" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30" s="2"/>
+      <c r="AK30" s="2"/>
+      <c r="AL30" s="2"/>
+    </row>
+    <row r="31" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6"/>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="6"/>
-      <c r="AB31" s="6"/>
-      <c r="AC31" s="6"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
       <c r="AL31" s="1"/>
     </row>
-    <row r="32" spans="1:38" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="22"/>
-      <c r="B32" s="23" t="s">
+    <row r="32" spans="1:38" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+    </row>
+    <row r="33" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="17"/>
+      <c r="B33" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="23"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="24"/>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-      <c r="O32" s="24"/>
-      <c r="P32" s="24"/>
-      <c r="Q32" s="24"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="51" t="s">
+      <c r="C33" s="18"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="19"/>
+      <c r="M33" s="19"/>
+      <c r="N33" s="19"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="19"/>
+      <c r="Q33" s="19"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="T32" s="51"/>
-      <c r="U32" s="51"/>
-      <c r="V32" s="51"/>
-      <c r="W32" s="51"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="51"/>
-      <c r="AA32" s="51"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="51"/>
-      <c r="AE32" s="51"/>
-      <c r="AF32" s="51"/>
-      <c r="AG32" s="51"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22"/>
-    </row>
-    <row r="33" spans="1:38" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="22"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="59" t="s">
+      <c r="T33" s="46"/>
+      <c r="U33" s="46"/>
+      <c r="V33" s="46"/>
+      <c r="W33" s="46"/>
+      <c r="X33" s="46"/>
+      <c r="Y33" s="46"/>
+      <c r="Z33" s="46"/>
+      <c r="AA33" s="46"/>
+      <c r="AB33" s="46"/>
+      <c r="AC33" s="46"/>
+      <c r="AD33" s="46"/>
+      <c r="AE33" s="46"/>
+      <c r="AF33" s="46"/>
+      <c r="AG33" s="46"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="17"/>
+      <c r="AJ33" s="17"/>
+      <c r="AK33" s="17"/>
+      <c r="AL33" s="17"/>
+    </row>
+    <row r="34" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K33" s="60"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="60"/>
-      <c r="N33" s="60"/>
-      <c r="O33" s="60"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="58" t="s">
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="17"/>
+      <c r="S34" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="T33" s="58"/>
-      <c r="U33" s="58"/>
-      <c r="V33" s="58"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="58"/>
-      <c r="Y33" s="58"/>
-      <c r="Z33" s="58"/>
-      <c r="AA33" s="58"/>
-      <c r="AB33" s="58"/>
-      <c r="AC33" s="58"/>
-      <c r="AD33" s="58"/>
-      <c r="AE33" s="58"/>
-      <c r="AF33" s="58"/>
-      <c r="AG33" s="58"/>
-      <c r="AH33" s="22"/>
-      <c r="AI33" s="22"/>
-      <c r="AJ33" s="22"/>
-      <c r="AK33" s="22"/>
-      <c r="AL33" s="22"/>
-    </row>
-    <row r="34" spans="1:38" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="22"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-      <c r="X34" s="22"/>
-      <c r="Y34" s="22"/>
-      <c r="Z34" s="22"/>
-      <c r="AA34" s="22"/>
-      <c r="AB34" s="22"/>
-      <c r="AC34" s="22"/>
-      <c r="AD34" s="22"/>
-      <c r="AE34" s="22"/>
-      <c r="AF34" s="22"/>
-      <c r="AG34" s="22"/>
-      <c r="AH34" s="22"/>
-      <c r="AI34" s="22"/>
-      <c r="AJ34" s="22"/>
-      <c r="AK34" s="22"/>
-      <c r="AL34" s="22"/>
-    </row>
-    <row r="35" spans="1:38" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="22"/>
-      <c r="B35" s="23" t="s">
+      <c r="T34" s="31"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="31"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="31"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="17"/>
+      <c r="AI34" s="17"/>
+      <c r="AJ34" s="17"/>
+      <c r="AK34" s="17"/>
+      <c r="AL34" s="17"/>
+    </row>
+    <row r="35" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17"/>
+      <c r="P35" s="17"/>
+      <c r="Q35" s="17"/>
+      <c r="R35" s="17"/>
+      <c r="S35" s="17"/>
+      <c r="T35" s="17"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="17"/>
+      <c r="AB35" s="17"/>
+      <c r="AC35" s="17"/>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+      <c r="AF35" s="17"/>
+      <c r="AG35" s="17"/>
+      <c r="AH35" s="17"/>
+      <c r="AI35" s="17"/>
+      <c r="AJ35" s="17"/>
+      <c r="AK35" s="17"/>
+      <c r="AL35" s="17"/>
+    </row>
+    <row r="36" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="23"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="24"/>
-      <c r="K35" s="24"/>
-      <c r="L35" s="24"/>
-      <c r="M35" s="24"/>
-      <c r="N35" s="24"/>
-      <c r="O35" s="24"/>
-      <c r="P35" s="24"/>
-      <c r="Q35" s="24"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="51"/>
-      <c r="T35" s="51"/>
-      <c r="U35" s="51"/>
-      <c r="V35" s="51"/>
-      <c r="W35" s="51"/>
-      <c r="X35" s="51"/>
-      <c r="Y35" s="51"/>
-      <c r="Z35" s="51"/>
-      <c r="AA35" s="51"/>
-      <c r="AB35" s="51"/>
-      <c r="AC35" s="51"/>
-      <c r="AD35" s="51"/>
-      <c r="AE35" s="51"/>
-      <c r="AF35" s="51"/>
-      <c r="AG35" s="51"/>
-      <c r="AH35" s="22"/>
-      <c r="AI35" s="22"/>
-      <c r="AJ35" s="22"/>
-      <c r="AK35" s="22"/>
-      <c r="AL35" s="22"/>
-    </row>
-    <row r="36" spans="1:38" s="25" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="22"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="59" t="s">
+      <c r="C36" s="18"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="19"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="19"/>
+      <c r="Q36" s="19"/>
+      <c r="R36" s="17"/>
+      <c r="S36" s="46"/>
+      <c r="T36" s="46"/>
+      <c r="U36" s="46"/>
+      <c r="V36" s="46"/>
+      <c r="W36" s="46"/>
+      <c r="X36" s="46"/>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="46"/>
+      <c r="AA36" s="46"/>
+      <c r="AB36" s="46"/>
+      <c r="AC36" s="46"/>
+      <c r="AD36" s="46"/>
+      <c r="AE36" s="46"/>
+      <c r="AF36" s="46"/>
+      <c r="AG36" s="46"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="17"/>
+      <c r="AL36" s="17"/>
+    </row>
+    <row r="37" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K36" s="60"/>
-      <c r="L36" s="60"/>
-      <c r="M36" s="60"/>
-      <c r="N36" s="60"/>
-      <c r="O36" s="60"/>
-      <c r="P36" s="60"/>
-      <c r="Q36" s="60"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="58" t="s">
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="17"/>
+      <c r="S37" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="T36" s="58"/>
-      <c r="U36" s="58"/>
-      <c r="V36" s="58"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="58"/>
-      <c r="Y36" s="58"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="58"/>
-      <c r="AB36" s="58"/>
-      <c r="AC36" s="58"/>
-      <c r="AD36" s="58"/>
-      <c r="AE36" s="58"/>
-      <c r="AF36" s="58"/>
-      <c r="AG36" s="58"/>
-      <c r="AH36" s="22"/>
-      <c r="AI36" s="22"/>
-      <c r="AJ36" s="22"/>
-      <c r="AK36" s="22"/>
-      <c r="AL36" s="22"/>
-    </row>
-    <row r="37" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1"/>
-      <c r="AE37" s="1"/>
-      <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-      <c r="AH37" s="1"/>
-      <c r="AI37" s="1"/>
-      <c r="AJ37" s="1"/>
-      <c r="AK37" s="1"/>
-      <c r="AL37" s="1"/>
-    </row>
-    <row r="38" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
+      <c r="AA37" s="31"/>
+      <c r="AB37" s="31"/>
+      <c r="AC37" s="31"/>
+      <c r="AD37" s="31"/>
+      <c r="AE37" s="31"/>
+      <c r="AF37" s="31"/>
+      <c r="AG37" s="31"/>
+      <c r="AH37" s="17"/>
+      <c r="AI37" s="17"/>
+      <c r="AJ37" s="17"/>
+      <c r="AK37" s="17"/>
+      <c r="AL37" s="17"/>
+    </row>
+    <row r="38" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2802,7 +2765,9 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="17" t="s">
+        <v>37</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
@@ -41145,58 +41110,98 @@
       <c r="AK996" s="1"/>
       <c r="AL996" s="1"/>
     </row>
+    <row r="997" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A997" s="1"/>
+      <c r="B997" s="1"/>
+      <c r="C997" s="1"/>
+      <c r="D997" s="1"/>
+      <c r="E997" s="1"/>
+      <c r="F997" s="1"/>
+      <c r="G997" s="1"/>
+      <c r="H997" s="1"/>
+      <c r="I997" s="1"/>
+      <c r="J997" s="1"/>
+      <c r="K997" s="1"/>
+      <c r="L997" s="1"/>
+      <c r="M997" s="1"/>
+      <c r="N997" s="1"/>
+      <c r="O997" s="1"/>
+      <c r="P997" s="1"/>
+      <c r="Q997" s="1"/>
+      <c r="R997" s="1"/>
+      <c r="S997" s="1"/>
+      <c r="T997" s="1"/>
+      <c r="U997" s="1"/>
+      <c r="V997" s="1"/>
+      <c r="W997" s="1"/>
+      <c r="X997" s="1"/>
+      <c r="Y997" s="1"/>
+      <c r="Z997" s="1"/>
+      <c r="AA997" s="1"/>
+      <c r="AB997" s="1"/>
+      <c r="AC997" s="1"/>
+      <c r="AD997" s="1"/>
+      <c r="AE997" s="1"/>
+      <c r="AF997" s="1"/>
+      <c r="AG997" s="1"/>
+      <c r="AH997" s="1"/>
+      <c r="AI997" s="1"/>
+      <c r="AJ997" s="1"/>
+      <c r="AK997" s="1"/>
+      <c r="AL997" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="B5:N6"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="O5:R6"/>
+    <mergeCell ref="S5:AB6"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="O2:R4"/>
+    <mergeCell ref="S2:AB4"/>
+    <mergeCell ref="B2:N4"/>
+    <mergeCell ref="S36:AG36"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:AL14"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="B29:AJ29"/>
+    <mergeCell ref="G19:AL19"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="J34:Q34"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="S33:AG33"/>
+    <mergeCell ref="D22:R22"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Z23:AE23"/>
+    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B28:AL28"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="D23:R23"/>
     <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="D20:R20"/>
-    <mergeCell ref="Z20:AE20"/>
-    <mergeCell ref="S20:V20"/>
-    <mergeCell ref="J36:Q36"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B11:N11"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
     <mergeCell ref="S21:V21"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="AF20:AK20"/>
-    <mergeCell ref="B27:AL27"/>
-    <mergeCell ref="B14:AL14"/>
-    <mergeCell ref="D22:R22"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B10:N10"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S35:AG35"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:AL13"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B28:AJ28"/>
-    <mergeCell ref="G18:AL18"/>
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="J33:Q33"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="S32:AG32"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Z22:AE22"/>
-    <mergeCell ref="G16:AL16"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B7:N9"/>
-    <mergeCell ref="AC10:AL10"/>
-    <mergeCell ref="O6:R10"/>
-    <mergeCell ref="AD2:AJ9"/>
-    <mergeCell ref="B2:N4"/>
-    <mergeCell ref="O2:R3"/>
-    <mergeCell ref="S2:AB3"/>
-    <mergeCell ref="O4:R5"/>
-    <mergeCell ref="S4:AB5"/>
-    <mergeCell ref="B5:N5"/>
-    <mergeCell ref="S6:AB10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BE2BEF-BB97-4C07-8D3D-522ABF4EAC4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A8918B-A82D-4C41-948D-BC8B9AAB83B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>{{БАНК_КОРРСЧЕТ}}</t>
-  </si>
-  <si>
-    <t>Банк</t>
   </si>
   <si>
     <t>ИНН</t>
@@ -167,6 +164,9 @@
   </si>
   <si>
     <t>{{КОМПАНИЯ}}, ИНН: {{КОМПАНИЯ_ИНН}}, ИНН РФ: {{КОМПАНИЯ_ИНН_РФ}}, ОКПО: {{КОМПАНИЯ_ОКПО}}, {{КОМПАНИЯ_АДРЕС}}</t>
+  </si>
+  <si>
+    <t>Банк получателя</t>
   </si>
 </sst>
 </file>
@@ -580,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -600,7 +600,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -626,108 +625,30 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -739,25 +660,7 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -766,20 +669,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -805,26 +699,80 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -835,6 +783,49 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1198,435 +1189,435 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="73"/>
-      <c r="O2" s="62" t="s">
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="76" t="s">
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="78"/>
-      <c r="AC2" s="88"/>
-      <c r="AD2" s="89"/>
-      <c r="AE2" s="89"/>
-      <c r="AF2" s="89"/>
-      <c r="AG2" s="89"/>
-      <c r="AH2" s="89"/>
-      <c r="AI2" s="89"/>
-      <c r="AJ2" s="89"/>
-      <c r="AK2" s="89"/>
-      <c r="AL2" s="90"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="22"/>
+      <c r="AD2" s="22"/>
+      <c r="AE2" s="22"/>
+      <c r="AF2" s="22"/>
+      <c r="AG2" s="22"/>
+      <c r="AH2" s="22"/>
+      <c r="AI2" s="22"/>
+      <c r="AJ2" s="22"/>
+      <c r="AK2" s="22"/>
+      <c r="AL2" s="23"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
-      <c r="L3" s="56"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="87"/>
-      <c r="T3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Y3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="84"/>
-      <c r="AD3" s="72" t="s">
-        <v>40</v>
+      <c r="B3" s="29"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="46"/>
+      <c r="V3" s="46"/>
+      <c r="W3" s="46"/>
+      <c r="X3" s="46"/>
+      <c r="Y3" s="46"/>
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="46"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="38" t="s">
+        <v>39</v>
       </c>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="86"/>
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="38"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
+      <c r="AK3" s="20"/>
+      <c r="AL3" s="21"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="69"/>
-      <c r="Q4" s="69"/>
-      <c r="R4" s="70"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="81"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="46"/>
+      <c r="U4" s="46"/>
+      <c r="V4" s="46"/>
+      <c r="W4" s="46"/>
+      <c r="X4" s="46"/>
+      <c r="Y4" s="46"/>
+      <c r="Z4" s="46"/>
+      <c r="AA4" s="46"/>
+      <c r="AB4" s="47"/>
       <c r="AC4" s="9"/>
-      <c r="AD4" s="72"/>
-      <c r="AE4" s="72"/>
-      <c r="AF4" s="72"/>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="72"/>
-      <c r="AI4" s="72"/>
-      <c r="AJ4" s="72"/>
-      <c r="AK4" s="10"/>
-      <c r="AL4" s="11"/>
+      <c r="AD4" s="38"/>
+      <c r="AE4" s="38"/>
+      <c r="AF4" s="38"/>
+      <c r="AG4" s="38"/>
+      <c r="AH4" s="38"/>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="38"/>
+      <c r="AK4" s="9"/>
+      <c r="AL4" s="10"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="65" t="s">
+      <c r="B5" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86"/>
+      <c r="E5" s="86"/>
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="86"/>
+      <c r="N5" s="86"/>
+      <c r="O5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="T5" s="46"/>
+      <c r="U5" s="46"/>
+      <c r="V5" s="46"/>
+      <c r="W5" s="46"/>
+      <c r="X5" s="46"/>
+      <c r="Y5" s="46"/>
+      <c r="Z5" s="46"/>
+      <c r="AA5" s="46"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="38"/>
+      <c r="AF5" s="38"/>
+      <c r="AG5" s="38"/>
+      <c r="AH5" s="38"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="13"/>
+    </row>
+    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
+      <c r="B6" s="92"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="93"/>
+      <c r="E6" s="93"/>
+      <c r="F6" s="93"/>
+      <c r="G6" s="93"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="93"/>
+      <c r="J6" s="93"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="93"/>
+      <c r="M6" s="93"/>
+      <c r="N6" s="93"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="44"/>
+      <c r="V6" s="44"/>
+      <c r="W6" s="44"/>
+      <c r="X6" s="44"/>
+      <c r="Y6" s="44"/>
+      <c r="Z6" s="44"/>
+      <c r="AA6" s="44"/>
+      <c r="AB6" s="45"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="14"/>
+    </row>
+    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="62" t="s">
+      <c r="C7" s="88"/>
+      <c r="D7" s="38" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="89"/>
+      <c r="K7" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="76" t="s">
-        <v>4</v>
-      </c>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="78"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="72"/>
-      <c r="AE5" s="72"/>
-      <c r="AF5" s="72"/>
-      <c r="AG5" s="72"/>
-      <c r="AH5" s="72"/>
-      <c r="AI5" s="72"/>
-      <c r="AJ5" s="72"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="14"/>
-    </row>
-    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="65"/>
-      <c r="P6" s="66"/>
-      <c r="Q6" s="66"/>
-      <c r="R6" s="67"/>
-      <c r="S6" s="79"/>
-      <c r="T6" s="80"/>
-      <c r="U6" s="80"/>
-      <c r="V6" s="80"/>
-      <c r="W6" s="80"/>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="80"/>
-      <c r="Z6" s="80"/>
-      <c r="AA6" s="80"/>
-      <c r="AB6" s="81"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="72"/>
-      <c r="AF6" s="72"/>
-      <c r="AG6" s="72"/>
-      <c r="AH6" s="72"/>
-      <c r="AI6" s="72"/>
-      <c r="AJ6" s="72"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="15"/>
-    </row>
-    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="91" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="71"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="71"/>
-      <c r="H7" s="71"/>
-      <c r="I7" s="93" t="s">
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="94" t="s">
+      <c r="T7" s="46"/>
+      <c r="U7" s="46"/>
+      <c r="V7" s="46"/>
+      <c r="W7" s="46"/>
+      <c r="X7" s="46"/>
+      <c r="Y7" s="46"/>
+      <c r="Z7" s="46"/>
+      <c r="AA7" s="46"/>
+      <c r="AB7" s="47"/>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="38"/>
+      <c r="AE7" s="38"/>
+      <c r="AF7" s="38"/>
+      <c r="AG7" s="38"/>
+      <c r="AH7" s="38"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="38"/>
+      <c r="AK7" s="12"/>
+      <c r="AL7" s="14"/>
+    </row>
+    <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
+      <c r="B8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="26"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+      <c r="V8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="46"/>
+      <c r="Y8" s="46"/>
+      <c r="Z8" s="46"/>
+      <c r="AA8" s="46"/>
+      <c r="AB8" s="47"/>
+      <c r="AC8" s="11"/>
+      <c r="AD8" s="38"/>
+      <c r="AE8" s="38"/>
+      <c r="AF8" s="38"/>
+      <c r="AG8" s="38"/>
+      <c r="AH8" s="38"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="38"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="14"/>
+    </row>
+    <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="46"/>
+      <c r="T9" s="46"/>
+      <c r="U9" s="46"/>
+      <c r="V9" s="46"/>
+      <c r="W9" s="46"/>
+      <c r="X9" s="46"/>
+      <c r="Y9" s="46"/>
+      <c r="Z9" s="46"/>
+      <c r="AA9" s="46"/>
+      <c r="AB9" s="47"/>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="38"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="14"/>
+    </row>
+    <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="46"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="46"/>
+      <c r="V10" s="46"/>
+      <c r="W10" s="46"/>
+      <c r="X10" s="46"/>
+      <c r="Y10" s="46"/>
+      <c r="Z10" s="46"/>
+      <c r="AA10" s="46"/>
+      <c r="AB10" s="47"/>
+      <c r="AC10" s="11"/>
+      <c r="AD10" s="38"/>
+      <c r="AE10" s="38"/>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="14"/>
+    </row>
+    <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
+      <c r="B11" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="77"/>
+      <c r="G11" s="77"/>
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="37"/>
+      <c r="S11" s="44"/>
+      <c r="T11" s="44"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="44"/>
+      <c r="W11" s="44"/>
+      <c r="X11" s="44"/>
+      <c r="Y11" s="44"/>
+      <c r="Z11" s="44"/>
+      <c r="AA11" s="44"/>
+      <c r="AB11" s="45"/>
+      <c r="AC11" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="L7" s="94"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="95"/>
-      <c r="O7" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="63"/>
-      <c r="Q7" s="63"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="77" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="77"/>
-      <c r="U7" s="77"/>
-      <c r="V7" s="77"/>
-      <c r="W7" s="77"/>
-      <c r="X7" s="77"/>
-      <c r="Y7" s="77"/>
-      <c r="Z7" s="77"/>
-      <c r="AA7" s="77"/>
-      <c r="AB7" s="78"/>
-      <c r="AC7" s="12"/>
-      <c r="AD7" s="72"/>
-      <c r="AE7" s="72"/>
-      <c r="AF7" s="72"/>
-      <c r="AG7" s="72"/>
-      <c r="AH7" s="72"/>
-      <c r="AI7" s="72"/>
-      <c r="AJ7" s="72"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="15"/>
-    </row>
-    <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="55" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="74"/>
-      <c r="O8" s="66"/>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="82"/>
-      <c r="T8" s="82"/>
-      <c r="U8" s="82"/>
-      <c r="V8" s="82"/>
-      <c r="W8" s="82"/>
-      <c r="X8" s="82"/>
-      <c r="Y8" s="82"/>
-      <c r="Z8" s="82"/>
-      <c r="AA8" s="82"/>
-      <c r="AB8" s="83"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="72"/>
-      <c r="AE8" s="72"/>
-      <c r="AF8" s="72"/>
-      <c r="AG8" s="72"/>
-      <c r="AH8" s="72"/>
-      <c r="AI8" s="72"/>
-      <c r="AJ8" s="72"/>
-      <c r="AK8" s="13"/>
-      <c r="AL8" s="15"/>
-    </row>
-    <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="56"/>
-      <c r="E9" s="56"/>
-      <c r="F9" s="56"/>
-      <c r="G9" s="56"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="74"/>
-      <c r="O9" s="66"/>
-      <c r="P9" s="66"/>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="67"/>
-      <c r="S9" s="82"/>
-      <c r="T9" s="82"/>
-      <c r="U9" s="82"/>
-      <c r="V9" s="82"/>
-      <c r="W9" s="82"/>
-      <c r="X9" s="82"/>
-      <c r="Y9" s="82"/>
-      <c r="Z9" s="82"/>
-      <c r="AA9" s="82"/>
-      <c r="AB9" s="83"/>
-      <c r="AC9" s="12"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="72"/>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="72"/>
-      <c r="AJ9" s="72"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="15"/>
-    </row>
-    <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="74"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="67"/>
-      <c r="S10" s="82"/>
-      <c r="T10" s="82"/>
-      <c r="U10" s="82"/>
-      <c r="V10" s="82"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="82"/>
-      <c r="Y10" s="82"/>
-      <c r="Z10" s="82"/>
-      <c r="AA10" s="82"/>
-      <c r="AB10" s="83"/>
-      <c r="AC10" s="12"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72"/>
-      <c r="AK10" s="13"/>
-      <c r="AL10" s="15"/>
-    </row>
-    <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1"/>
-      <c r="B11" s="96" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
-      <c r="N11" s="98"/>
-      <c r="O11" s="69"/>
-      <c r="P11" s="69"/>
-      <c r="Q11" s="69"/>
-      <c r="R11" s="70"/>
-      <c r="S11" s="80"/>
-      <c r="T11" s="80"/>
-      <c r="U11" s="80"/>
-      <c r="V11" s="80"/>
-      <c r="W11" s="80"/>
-      <c r="X11" s="80"/>
-      <c r="Y11" s="80"/>
-      <c r="Z11" s="80"/>
-      <c r="AA11" s="80"/>
-      <c r="AB11" s="81"/>
-      <c r="AC11" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="AD11" s="60"/>
-      <c r="AE11" s="60"/>
-      <c r="AF11" s="60"/>
-      <c r="AG11" s="60"/>
-      <c r="AH11" s="60"/>
-      <c r="AI11" s="60"/>
-      <c r="AJ11" s="60"/>
-      <c r="AK11" s="60"/>
-      <c r="AL11" s="61"/>
+      <c r="AD11" s="33"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="33"/>
+      <c r="AH11" s="33"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="33"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="34"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1670,125 +1661,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="47" t="s">
-        <v>12</v>
+      <c r="B13" s="55" t="s">
+        <v>11</v>
       </c>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
-      <c r="T13" s="47"/>
-      <c r="U13" s="47"/>
-      <c r="V13" s="47"/>
-      <c r="W13" s="47"/>
-      <c r="X13" s="47"/>
-      <c r="Y13" s="47"/>
-      <c r="Z13" s="47"/>
-      <c r="AA13" s="47"/>
-      <c r="AB13" s="47"/>
-      <c r="AC13" s="47"/>
-      <c r="AD13" s="47"/>
-      <c r="AE13" s="47"/>
-      <c r="AF13" s="47"/>
-      <c r="AG13" s="47"/>
-      <c r="AH13" s="47"/>
-      <c r="AI13" s="47"/>
-      <c r="AJ13" s="47"/>
-      <c r="AK13" s="47"/>
-      <c r="AL13" s="47"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="55"/>
+      <c r="Q13" s="55"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="55"/>
+      <c r="W13" s="55"/>
+      <c r="X13" s="55"/>
+      <c r="Y13" s="55"/>
+      <c r="Z13" s="55"/>
+      <c r="AA13" s="55"/>
+      <c r="AB13" s="55"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="55"/>
+      <c r="AE13" s="55"/>
+      <c r="AF13" s="55"/>
+      <c r="AG13" s="55"/>
+      <c r="AH13" s="55"/>
+      <c r="AI13" s="55"/>
+      <c r="AJ13" s="55"/>
+      <c r="AK13" s="55"/>
+      <c r="AL13" s="55"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
-      <c r="T14" s="47"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="47"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="47"/>
-      <c r="AC14" s="47"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="47"/>
-      <c r="AF14" s="47"/>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="47"/>
-      <c r="AI14" s="47"/>
-      <c r="AJ14" s="47"/>
-      <c r="AK14" s="47"/>
-      <c r="AL14" s="47"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="55"/>
+      <c r="M14" s="55"/>
+      <c r="N14" s="55"/>
+      <c r="O14" s="55"/>
+      <c r="P14" s="55"/>
+      <c r="Q14" s="55"/>
+      <c r="R14" s="55"/>
+      <c r="S14" s="55"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="55"/>
+      <c r="V14" s="55"/>
+      <c r="W14" s="55"/>
+      <c r="X14" s="55"/>
+      <c r="Y14" s="55"/>
+      <c r="Z14" s="55"/>
+      <c r="AA14" s="55"/>
+      <c r="AB14" s="55"/>
+      <c r="AC14" s="55"/>
+      <c r="AD14" s="55"/>
+      <c r="AE14" s="55"/>
+      <c r="AF14" s="55"/>
+      <c r="AG14" s="55"/>
+      <c r="AH14" s="55"/>
+      <c r="AI14" s="55"/>
+      <c r="AJ14" s="55"/>
+      <c r="AK14" s="55"/>
+      <c r="AL14" s="55"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="38"/>
-      <c r="S15" s="38"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="38"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="38"/>
-      <c r="Y15" s="38"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="38"/>
-      <c r="AB15" s="38"/>
-      <c r="AC15" s="38"/>
-      <c r="AD15" s="38"/>
-      <c r="AE15" s="38"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="38"/>
-      <c r="AH15" s="38"/>
-      <c r="AI15" s="38"/>
-      <c r="AJ15" s="38"/>
-      <c r="AK15" s="38"/>
-      <c r="AL15" s="38"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="73"/>
+      <c r="D15" s="73"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="73"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="73"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="73"/>
+      <c r="P15" s="73"/>
+      <c r="Q15" s="73"/>
+      <c r="R15" s="73"/>
+      <c r="S15" s="73"/>
+      <c r="T15" s="73"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="73"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="73"/>
+      <c r="AF15" s="73"/>
+      <c r="AG15" s="73"/>
+      <c r="AH15" s="73"/>
+      <c r="AI15" s="73"/>
+      <c r="AJ15" s="73"/>
+      <c r="AK15" s="73"/>
+      <c r="AL15" s="73"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1832,47 +1823,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="49" t="s">
-        <v>13</v>
+      <c r="B17" s="27" t="s">
+        <v>12</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="48" t="s">
-        <v>42</v>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="58" t="s">
+        <v>41</v>
       </c>
-      <c r="H17" s="48"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="48"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="48"/>
-      <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="48"/>
-      <c r="P17" s="48"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="48"/>
-      <c r="S17" s="48"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="48"/>
-      <c r="V17" s="48"/>
-      <c r="W17" s="48"/>
-      <c r="X17" s="48"/>
-      <c r="Y17" s="48"/>
-      <c r="Z17" s="48"/>
-      <c r="AA17" s="48"/>
-      <c r="AB17" s="48"/>
-      <c r="AC17" s="48"/>
-      <c r="AD17" s="48"/>
-      <c r="AE17" s="48"/>
-      <c r="AF17" s="48"/>
-      <c r="AG17" s="48"/>
-      <c r="AH17" s="48"/>
-      <c r="AI17" s="48"/>
-      <c r="AJ17" s="48"/>
-      <c r="AK17" s="48"/>
-      <c r="AL17" s="48"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="58"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="58"/>
+      <c r="S17" s="58"/>
+      <c r="T17" s="58"/>
+      <c r="U17" s="58"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="58"/>
+      <c r="X17" s="58"/>
+      <c r="Y17" s="58"/>
+      <c r="Z17" s="58"/>
+      <c r="AA17" s="58"/>
+      <c r="AB17" s="58"/>
+      <c r="AC17" s="58"/>
+      <c r="AD17" s="58"/>
+      <c r="AE17" s="58"/>
+      <c r="AF17" s="58"/>
+      <c r="AG17" s="58"/>
+      <c r="AH17" s="58"/>
+      <c r="AI17" s="58"/>
+      <c r="AJ17" s="58"/>
+      <c r="AK17" s="58"/>
+      <c r="AL17" s="58"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1916,47 +1907,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="48"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="48"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="48"/>
-      <c r="S19" s="48"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="48"/>
-      <c r="V19" s="48"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="48"/>
-      <c r="Y19" s="48"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="48"/>
-      <c r="AB19" s="48"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="48"/>
-      <c r="AE19" s="48"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="48"/>
-      <c r="AH19" s="48"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="48"/>
-      <c r="AK19" s="48"/>
-      <c r="AL19" s="48"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="58"/>
+      <c r="T19" s="58"/>
+      <c r="U19" s="58"/>
+      <c r="V19" s="58"/>
+      <c r="W19" s="58"/>
+      <c r="X19" s="58"/>
+      <c r="Y19" s="58"/>
+      <c r="Z19" s="58"/>
+      <c r="AA19" s="58"/>
+      <c r="AB19" s="58"/>
+      <c r="AC19" s="58"/>
+      <c r="AD19" s="58"/>
+      <c r="AE19" s="58"/>
+      <c r="AF19" s="58"/>
+      <c r="AG19" s="58"/>
+      <c r="AH19" s="58"/>
+      <c r="AI19" s="58"/>
+      <c r="AJ19" s="58"/>
+      <c r="AK19" s="58"/>
+      <c r="AL19" s="58"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2000,160 +1991,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="75" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="68"/>
+      <c r="D21" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="25"/>
-      <c r="D21" s="24" t="s">
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="68"/>
+      <c r="K21" s="68"/>
+      <c r="L21" s="68"/>
+      <c r="M21" s="68"/>
+      <c r="N21" s="68"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="68"/>
+      <c r="Q21" s="68"/>
+      <c r="R21" s="68"/>
+      <c r="S21" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
-      <c r="S21" s="24" t="s">
+      <c r="T21" s="68"/>
+      <c r="U21" s="68"/>
+      <c r="V21" s="68"/>
+      <c r="W21" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="24" t="s">
+      <c r="X21" s="68"/>
+      <c r="Y21" s="68"/>
+      <c r="Z21" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="26" t="s">
+      <c r="AA21" s="80"/>
+      <c r="AB21" s="80"/>
+      <c r="AC21" s="80"/>
+      <c r="AD21" s="80"/>
+      <c r="AE21" s="81"/>
+      <c r="AF21" s="70" t="s">
         <v>20</v>
       </c>
-      <c r="AA21" s="27"/>
-      <c r="AB21" s="27"/>
-      <c r="AC21" s="27"/>
-      <c r="AD21" s="27"/>
-      <c r="AE21" s="28"/>
-      <c r="AF21" s="35" t="s">
+      <c r="AG21" s="68"/>
+      <c r="AH21" s="68"/>
+      <c r="AI21" s="68"/>
+      <c r="AJ21" s="68"/>
+      <c r="AK21" s="71"/>
+      <c r="AL21" s="1"/>
+    </row>
+    <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="3"/>
+      <c r="B22" s="53">
+        <v>1</v>
+      </c>
+      <c r="C22" s="54"/>
+      <c r="D22" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="AG21" s="25"/>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="25"/>
-      <c r="AJ21" s="25"/>
-      <c r="AK21" s="36"/>
-      <c r="AL21" s="1"/>
-    </row>
-    <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="21">
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="54"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="54"/>
+      <c r="P22" s="54"/>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="69">
         <v>1</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="39" t="s">
+      <c r="T22" s="54"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="54"/>
+      <c r="W22" s="74" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="32">
-        <v>1</v>
-      </c>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="23" t="s">
+      <c r="X22" s="54"/>
+      <c r="Y22" s="54"/>
+      <c r="Z22" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="X22" s="22"/>
-      <c r="Y22" s="22"/>
-      <c r="Z22" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA22" s="44"/>
-      <c r="AB22" s="44"/>
-      <c r="AC22" s="44"/>
-      <c r="AD22" s="44"/>
-      <c r="AE22" s="45"/>
-      <c r="AF22" s="33" t="e">
+      <c r="AA22" s="83"/>
+      <c r="AB22" s="83"/>
+      <c r="AC22" s="83"/>
+      <c r="AD22" s="83"/>
+      <c r="AE22" s="84"/>
+      <c r="AF22" s="56" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="22"/>
-      <c r="AH22" s="22"/>
-      <c r="AI22" s="22"/>
-      <c r="AJ22" s="22"/>
-      <c r="AK22" s="34"/>
+      <c r="AG22" s="54"/>
+      <c r="AH22" s="54"/>
+      <c r="AI22" s="54"/>
+      <c r="AJ22" s="54"/>
+      <c r="AK22" s="57"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="21">
+      <c r="B23" s="53">
         <v>2</v>
       </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="39" t="s">
+      <c r="C23" s="54"/>
+      <c r="D23" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="69">
+        <v>1</v>
+      </c>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="32">
-        <v>1</v>
-      </c>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="X23" s="22"/>
-      <c r="Y23" s="22"/>
-      <c r="Z23" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA23" s="51"/>
-      <c r="AB23" s="51"/>
-      <c r="AC23" s="51"/>
-      <c r="AD23" s="51"/>
-      <c r="AE23" s="52"/>
-      <c r="AF23" s="33" t="e">
+      <c r="AA23" s="65"/>
+      <c r="AB23" s="65"/>
+      <c r="AC23" s="65"/>
+      <c r="AD23" s="65"/>
+      <c r="AE23" s="66"/>
+      <c r="AF23" s="56" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="22"/>
-      <c r="AH23" s="22"/>
-      <c r="AI23" s="22"/>
-      <c r="AJ23" s="22"/>
-      <c r="AK23" s="34"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54"/>
+      <c r="AK23" s="57"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2226,19 +2217,19 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
-      <c r="AD25" s="16"/>
-      <c r="AE25" s="16" t="s">
-        <v>27</v>
+      <c r="AD25" s="15"/>
+      <c r="AE25" s="15" t="s">
+        <v>26</v>
       </c>
-      <c r="AF25" s="41" t="e">
+      <c r="AF25" s="62" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="42"/>
-      <c r="AH25" s="42"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="42"/>
-      <c r="AK25" s="42"/>
+      <c r="AG25" s="28"/>
+      <c r="AH25" s="28"/>
+      <c r="AI25" s="28"/>
+      <c r="AJ25" s="28"/>
+      <c r="AK25" s="28"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2271,18 +2262,18 @@
       <c r="AA26" s="5"/>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
-      <c r="AD26" s="16"/>
-      <c r="AE26" s="16" t="s">
+      <c r="AD26" s="15"/>
+      <c r="AE26" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF26" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="AF26" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG26" s="42"/>
-      <c r="AH26" s="42"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="42"/>
-      <c r="AK26" s="42"/>
+      <c r="AG26" s="28"/>
+      <c r="AH26" s="28"/>
+      <c r="AI26" s="28"/>
+      <c r="AJ26" s="28"/>
+      <c r="AK26" s="28"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2315,102 +2306,102 @@
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
-      <c r="AD27" s="16"/>
-      <c r="AE27" s="16" t="s">
-        <v>30</v>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15" t="s">
+        <v>29</v>
       </c>
-      <c r="AF27" s="41" t="e">
+      <c r="AF27" s="62" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="42"/>
-      <c r="AH27" s="42"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="42"/>
-      <c r="AK27" s="42"/>
+      <c r="AG27" s="28"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="28"/>
+      <c r="AJ27" s="28"/>
+      <c r="AK27" s="28"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="72"/>
+      <c r="H28" s="72"/>
+      <c r="I28" s="72"/>
+      <c r="J28" s="72"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="72"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="72"/>
+      <c r="Q28" s="72"/>
+      <c r="R28" s="72"/>
+      <c r="S28" s="72"/>
+      <c r="T28" s="72"/>
+      <c r="U28" s="72"/>
+      <c r="V28" s="72"/>
+      <c r="W28" s="72"/>
+      <c r="X28" s="72"/>
+      <c r="Y28" s="72"/>
+      <c r="Z28" s="72"/>
+      <c r="AA28" s="72"/>
+      <c r="AB28" s="72"/>
+      <c r="AC28" s="72"/>
+      <c r="AD28" s="72"/>
+      <c r="AE28" s="72"/>
+      <c r="AF28" s="72"/>
+      <c r="AG28" s="72"/>
+      <c r="AH28" s="72"/>
+      <c r="AI28" s="72"/>
+      <c r="AJ28" s="72"/>
+      <c r="AK28" s="72"/>
+      <c r="AL28" s="72"/>
+    </row>
+    <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="37"/>
-      <c r="P28" s="37"/>
-      <c r="Q28" s="37"/>
-      <c r="R28" s="37"/>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="37"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="37"/>
-      <c r="AD28" s="37"/>
-      <c r="AE28" s="37"/>
-      <c r="AF28" s="37"/>
-      <c r="AG28" s="37"/>
-      <c r="AH28" s="37"/>
-      <c r="AI28" s="37"/>
-      <c r="AJ28" s="37"/>
-      <c r="AK28" s="37"/>
-      <c r="AL28" s="37"/>
-    </row>
-    <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="3"/>
-      <c r="B29" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="48"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="48"/>
-      <c r="H29" s="48"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="48"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="48"/>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="48"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="48"/>
-      <c r="W29" s="48"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="48"/>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="48"/>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="48"/>
-      <c r="AF29" s="48"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="48"/>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="48"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="58"/>
+      <c r="V29" s="58"/>
+      <c r="W29" s="58"/>
+      <c r="X29" s="58"/>
+      <c r="Y29" s="58"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="58"/>
+      <c r="AB29" s="58"/>
+      <c r="AC29" s="58"/>
+      <c r="AD29" s="58"/>
+      <c r="AE29" s="58"/>
+      <c r="AF29" s="58"/>
+      <c r="AG29" s="58"/>
+      <c r="AH29" s="58"/>
+      <c r="AI29" s="58"/>
+      <c r="AJ29" s="58"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2534,219 +2525,219 @@
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
-    <row r="33" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="18" t="s">
+    <row r="33" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16"/>
+      <c r="B33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" s="17"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="T33" s="52"/>
+      <c r="U33" s="52"/>
+      <c r="V33" s="52"/>
+      <c r="W33" s="52"/>
+      <c r="X33" s="52"/>
+      <c r="Y33" s="52"/>
+      <c r="Z33" s="52"/>
+      <c r="AA33" s="52"/>
+      <c r="AB33" s="52"/>
+      <c r="AC33" s="52"/>
+      <c r="AD33" s="52"/>
+      <c r="AE33" s="52"/>
+      <c r="AF33" s="52"/>
+      <c r="AG33" s="52"/>
+      <c r="AH33" s="16"/>
+      <c r="AI33" s="16"/>
+      <c r="AJ33" s="16"/>
+      <c r="AK33" s="16"/>
+      <c r="AL33" s="16"/>
+    </row>
+    <row r="34" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="19"/>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="17"/>
-      <c r="S33" s="46" t="s">
-        <v>41</v>
-      </c>
-      <c r="T33" s="46"/>
-      <c r="U33" s="46"/>
-      <c r="V33" s="46"/>
-      <c r="W33" s="46"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="46"/>
-      <c r="Z33" s="46"/>
-      <c r="AA33" s="46"/>
-      <c r="AB33" s="46"/>
-      <c r="AC33" s="46"/>
-      <c r="AD33" s="46"/>
-      <c r="AE33" s="46"/>
-      <c r="AF33" s="46"/>
-      <c r="AG33" s="46"/>
-      <c r="AH33" s="17"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="17"/>
-      <c r="AK33" s="17"/>
-      <c r="AL33" s="17"/>
-    </row>
-    <row r="34" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="29" t="s">
+      <c r="K34" s="61"/>
+      <c r="L34" s="61"/>
+      <c r="M34" s="61"/>
+      <c r="N34" s="61"/>
+      <c r="O34" s="61"/>
+      <c r="P34" s="61"/>
+      <c r="Q34" s="61"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="30"/>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="31" t="s">
+      <c r="T34" s="59"/>
+      <c r="U34" s="59"/>
+      <c r="V34" s="59"/>
+      <c r="W34" s="59"/>
+      <c r="X34" s="59"/>
+      <c r="Y34" s="59"/>
+      <c r="Z34" s="59"/>
+      <c r="AA34" s="59"/>
+      <c r="AB34" s="59"/>
+      <c r="AC34" s="59"/>
+      <c r="AD34" s="59"/>
+      <c r="AE34" s="59"/>
+      <c r="AF34" s="59"/>
+      <c r="AG34" s="59"/>
+      <c r="AH34" s="16"/>
+      <c r="AI34" s="16"/>
+      <c r="AJ34" s="16"/>
+      <c r="AK34" s="16"/>
+      <c r="AL34" s="16"/>
+    </row>
+    <row r="35" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="16"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+      <c r="AK35" s="16"/>
+      <c r="AL35" s="16"/>
+    </row>
+    <row r="36" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="T34" s="31"/>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
-      <c r="Y34" s="31"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="31"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="17"/>
-      <c r="AI34" s="17"/>
-      <c r="AJ34" s="17"/>
-      <c r="AK34" s="17"/>
-      <c r="AL34" s="17"/>
-    </row>
-    <row r="35" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-      <c r="K35" s="17"/>
-      <c r="L35" s="17"/>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17"/>
-      <c r="O35" s="17"/>
-      <c r="P35" s="17"/>
-      <c r="Q35" s="17"/>
-      <c r="R35" s="17"/>
-      <c r="S35" s="17"/>
-      <c r="T35" s="17"/>
-      <c r="U35" s="17"/>
-      <c r="V35" s="17"/>
-      <c r="W35" s="17"/>
-      <c r="X35" s="17"/>
-      <c r="Y35" s="17"/>
-      <c r="Z35" s="17"/>
-      <c r="AA35" s="17"/>
-      <c r="AB35" s="17"/>
-      <c r="AC35" s="17"/>
-      <c r="AD35" s="17"/>
-      <c r="AE35" s="17"/>
-      <c r="AF35" s="17"/>
-      <c r="AG35" s="17"/>
-      <c r="AH35" s="17"/>
-      <c r="AI35" s="17"/>
-      <c r="AJ35" s="17"/>
-      <c r="AK35" s="17"/>
-      <c r="AL35" s="17"/>
-    </row>
-    <row r="36" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="18" t="s">
-        <v>36</v>
+      <c r="C36" s="17"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="18"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
+      <c r="AA36" s="52"/>
+      <c r="AB36" s="52"/>
+      <c r="AC36" s="52"/>
+      <c r="AD36" s="52"/>
+      <c r="AE36" s="52"/>
+      <c r="AF36" s="52"/>
+      <c r="AG36" s="52"/>
+      <c r="AH36" s="16"/>
+      <c r="AI36" s="16"/>
+      <c r="AJ36" s="16"/>
+      <c r="AK36" s="16"/>
+      <c r="AL36" s="16"/>
+    </row>
+    <row r="37" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16"/>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="60" t="s">
+        <v>33</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="19"/>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="17"/>
-      <c r="S36" s="46"/>
-      <c r="T36" s="46"/>
-      <c r="U36" s="46"/>
-      <c r="V36" s="46"/>
-      <c r="W36" s="46"/>
-      <c r="X36" s="46"/>
-      <c r="Y36" s="46"/>
-      <c r="Z36" s="46"/>
-      <c r="AA36" s="46"/>
-      <c r="AB36" s="46"/>
-      <c r="AC36" s="46"/>
-      <c r="AD36" s="46"/>
-      <c r="AE36" s="46"/>
-      <c r="AF36" s="46"/>
-      <c r="AG36" s="46"/>
-      <c r="AH36" s="17"/>
-      <c r="AI36" s="17"/>
-      <c r="AJ36" s="17"/>
-      <c r="AK36" s="17"/>
-      <c r="AL36" s="17"/>
-    </row>
-    <row r="37" spans="1:38" s="20" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="29" t="s">
+      <c r="K37" s="61"/>
+      <c r="L37" s="61"/>
+      <c r="M37" s="61"/>
+      <c r="N37" s="61"/>
+      <c r="O37" s="61"/>
+      <c r="P37" s="61"/>
+      <c r="Q37" s="61"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="17"/>
-      <c r="S37" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="T37" s="31"/>
-      <c r="U37" s="31"/>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="31"/>
-      <c r="Y37" s="31"/>
-      <c r="Z37" s="31"/>
-      <c r="AA37" s="31"/>
-      <c r="AB37" s="31"/>
-      <c r="AC37" s="31"/>
-      <c r="AD37" s="31"/>
-      <c r="AE37" s="31"/>
-      <c r="AF37" s="31"/>
-      <c r="AG37" s="31"/>
-      <c r="AH37" s="17"/>
-      <c r="AI37" s="17"/>
-      <c r="AJ37" s="17"/>
-      <c r="AK37" s="17"/>
-      <c r="AL37" s="17"/>
+      <c r="T37" s="59"/>
+      <c r="U37" s="59"/>
+      <c r="V37" s="59"/>
+      <c r="W37" s="59"/>
+      <c r="X37" s="59"/>
+      <c r="Y37" s="59"/>
+      <c r="Z37" s="59"/>
+      <c r="AA37" s="59"/>
+      <c r="AB37" s="59"/>
+      <c r="AC37" s="59"/>
+      <c r="AD37" s="59"/>
+      <c r="AE37" s="59"/>
+      <c r="AF37" s="59"/>
+      <c r="AG37" s="59"/>
+      <c r="AH37" s="16"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="16"/>
+      <c r="AK37" s="16"/>
+      <c r="AL37" s="16"/>
     </row>
     <row r="38" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
@@ -2765,8 +2756,8 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="17" t="s">
-        <v>37</v>
+      <c r="Q38" s="16" t="s">
+        <v>36</v>
       </c>
       <c r="R38" s="1"/>
       <c r="S38" s="1"/>
@@ -41152,18 +41143,28 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B5:N6"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B8:N10"/>
-    <mergeCell ref="AC11:AL11"/>
-    <mergeCell ref="O7:R11"/>
-    <mergeCell ref="AD3:AJ10"/>
-    <mergeCell ref="O5:R6"/>
-    <mergeCell ref="S5:AB6"/>
-    <mergeCell ref="S7:AB11"/>
-    <mergeCell ref="O2:R4"/>
-    <mergeCell ref="S2:AB4"/>
-    <mergeCell ref="B2:N4"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B28:AL28"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B11:N11"/>
+    <mergeCell ref="K7:N7"/>
     <mergeCell ref="S36:AG36"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:AL14"/>
@@ -41180,31 +41181,21 @@
     <mergeCell ref="Z23:AE23"/>
     <mergeCell ref="G17:AL17"/>
     <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B28:AL28"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="D23:R23"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B11:N11"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="B5:N6"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="O5:R6"/>
+    <mergeCell ref="S5:AB6"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="O2:R4"/>
+    <mergeCell ref="S2:AB4"/>
+    <mergeCell ref="B2:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A8918B-A82D-4C41-948D-BC8B9AAB83B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190BC356-BA65-4DB9-B9BF-0A7EF4A41AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -580,7 +580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -630,18 +630,122 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -660,7 +764,10 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -669,10 +776,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -684,148 +815,29 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1189,39 +1201,39 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="39" t="s">
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="85" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="40" t="s">
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="42"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="88"/>
+      <c r="Y2" s="88"/>
+      <c r="Z2" s="88"/>
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="89"/>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22"/>
       <c r="AE2" s="22"/>
@@ -1235,389 +1247,389 @@
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="46"/>
-      <c r="U3" s="46"/>
-      <c r="V3" s="46"/>
-      <c r="W3" s="46"/>
-      <c r="X3" s="46"/>
-      <c r="Y3" s="46"/>
-      <c r="Z3" s="46"/>
-      <c r="AA3" s="46"/>
-      <c r="AB3" s="47"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="69"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="80"/>
+      <c r="U3" s="80"/>
+      <c r="V3" s="80"/>
+      <c r="W3" s="80"/>
+      <c r="X3" s="80"/>
+      <c r="Y3" s="80"/>
+      <c r="Z3" s="80"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="81"/>
       <c r="AC3" s="20"/>
-      <c r="AD3" s="38" t="s">
+      <c r="AD3" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="38"/>
-      <c r="AF3" s="38"/>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="38"/>
+      <c r="AE3" s="52"/>
+      <c r="AF3" s="52"/>
+      <c r="AG3" s="52"/>
+      <c r="AH3" s="52"/>
+      <c r="AI3" s="52"/>
+      <c r="AJ3" s="52"/>
       <c r="AK3" s="20"/>
       <c r="AL3" s="21"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
-      <c r="S4" s="49"/>
-      <c r="T4" s="46"/>
-      <c r="U4" s="46"/>
-      <c r="V4" s="46"/>
-      <c r="W4" s="46"/>
-      <c r="X4" s="46"/>
-      <c r="Y4" s="46"/>
-      <c r="Z4" s="46"/>
-      <c r="AA4" s="46"/>
-      <c r="AB4" s="47"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="69"/>
+      <c r="O4" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="74"/>
+      <c r="S4" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="80"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="80"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="81"/>
       <c r="AC4" s="9"/>
-      <c r="AD4" s="38"/>
-      <c r="AE4" s="38"/>
-      <c r="AF4" s="38"/>
-      <c r="AG4" s="38"/>
-      <c r="AH4" s="38"/>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="38"/>
+      <c r="AD4" s="52"/>
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="52"/>
+      <c r="AG4" s="52"/>
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
       <c r="AK4" s="9"/>
       <c r="AL4" s="10"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="69"/>
+      <c r="O5" s="77"/>
+      <c r="P5" s="73"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="79"/>
+      <c r="T5" s="80"/>
+      <c r="U5" s="80"/>
+      <c r="V5" s="80"/>
+      <c r="W5" s="80"/>
+      <c r="X5" s="80"/>
+      <c r="Y5" s="80"/>
+      <c r="Z5" s="80"/>
+      <c r="AA5" s="80"/>
+      <c r="AB5" s="81"/>
+      <c r="AC5" s="12"/>
+      <c r="AD5" s="52"/>
+      <c r="AE5" s="52"/>
+      <c r="AF5" s="52"/>
+      <c r="AG5" s="52"/>
+      <c r="AH5" s="52"/>
+      <c r="AI5" s="52"/>
+      <c r="AJ5" s="52"/>
+      <c r="AK5" s="12"/>
+      <c r="AL5" s="13"/>
+    </row>
+    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
-      <c r="F5" s="86"/>
-      <c r="G5" s="86"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="86"/>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="86"/>
-      <c r="M5" s="86"/>
-      <c r="N5" s="86"/>
-      <c r="O5" s="24" t="s">
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
+      <c r="L6" s="66"/>
+      <c r="M6" s="66"/>
+      <c r="N6" s="92"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="75"/>
+      <c r="Q6" s="75"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="82"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="83"/>
+      <c r="Z6" s="83"/>
+      <c r="AA6" s="83"/>
+      <c r="AB6" s="84"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="52"/>
+      <c r="AE6" s="52"/>
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="52"/>
+      <c r="AH6" s="52"/>
+      <c r="AI6" s="52"/>
+      <c r="AJ6" s="52"/>
+      <c r="AK6" s="12"/>
+      <c r="AL6" s="14"/>
+    </row>
+    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="J7" s="41"/>
+      <c r="K7" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="49" t="s">
-        <v>4</v>
-      </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="46"/>
-      <c r="V5" s="46"/>
-      <c r="W5" s="46"/>
-      <c r="X5" s="46"/>
-      <c r="Y5" s="46"/>
-      <c r="Z5" s="46"/>
-      <c r="AA5" s="46"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="38"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="38"/>
-      <c r="AH5" s="38"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="38"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="13"/>
-    </row>
-    <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="92"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="93"/>
-      <c r="K6" s="93"/>
-      <c r="L6" s="93"/>
-      <c r="M6" s="93"/>
-      <c r="N6" s="93"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="44"/>
-      <c r="AA6" s="44"/>
-      <c r="AB6" s="45"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="38"/>
-      <c r="AE6" s="38"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
-      <c r="AH6" s="38"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="38"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="14"/>
-    </row>
-    <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="87" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="88"/>
-      <c r="D7" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="89" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7" s="89"/>
-      <c r="K7" s="90" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="26"/>
-      <c r="S7" s="46" t="s">
+      <c r="P7" s="73"/>
+      <c r="Q7" s="73"/>
+      <c r="R7" s="74"/>
+      <c r="S7" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="47"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="80"/>
+      <c r="W7" s="80"/>
+      <c r="X7" s="80"/>
+      <c r="Y7" s="80"/>
+      <c r="Z7" s="80"/>
+      <c r="AA7" s="80"/>
+      <c r="AB7" s="81"/>
       <c r="AC7" s="11"/>
-      <c r="AD7" s="38"/>
-      <c r="AE7" s="38"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="38"/>
-      <c r="AH7" s="38"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="38"/>
+      <c r="AD7" s="52"/>
+      <c r="AE7" s="52"/>
+      <c r="AF7" s="52"/>
+      <c r="AG7" s="52"/>
+      <c r="AH7" s="52"/>
+      <c r="AI7" s="52"/>
+      <c r="AJ7" s="52"/>
       <c r="AK7" s="12"/>
       <c r="AL7" s="14"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="31"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="26"/>
-      <c r="S8" s="46"/>
-      <c r="T8" s="46"/>
-      <c r="U8" s="46"/>
-      <c r="V8" s="46"/>
-      <c r="W8" s="46"/>
-      <c r="X8" s="46"/>
-      <c r="Y8" s="46"/>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="46"/>
-      <c r="AB8" s="47"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="96"/>
+      <c r="K8" s="96"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
+      <c r="N8" s="97"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="73"/>
+      <c r="R8" s="74"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="80"/>
+      <c r="U8" s="80"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="80"/>
+      <c r="X8" s="80"/>
+      <c r="Y8" s="80"/>
+      <c r="Z8" s="80"/>
+      <c r="AA8" s="80"/>
+      <c r="AB8" s="81"/>
       <c r="AC8" s="11"/>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="38"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="38"/>
-      <c r="AH8" s="38"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="38"/>
+      <c r="AD8" s="52"/>
+      <c r="AE8" s="52"/>
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="52"/>
+      <c r="AH8" s="52"/>
+      <c r="AI8" s="52"/>
+      <c r="AJ8" s="52"/>
       <c r="AK8" s="12"/>
       <c r="AL8" s="14"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="26"/>
-      <c r="S9" s="46"/>
-      <c r="T9" s="46"/>
-      <c r="U9" s="46"/>
-      <c r="V9" s="46"/>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46"/>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="46"/>
-      <c r="AB9" s="47"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="97"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="74"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="80"/>
+      <c r="Z9" s="80"/>
+      <c r="AA9" s="80"/>
+      <c r="AB9" s="81"/>
       <c r="AC9" s="11"/>
-      <c r="AD9" s="38"/>
-      <c r="AE9" s="38"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="38"/>
-      <c r="AH9" s="38"/>
-      <c r="AI9" s="38"/>
-      <c r="AJ9" s="38"/>
+      <c r="AD9" s="52"/>
+      <c r="AE9" s="52"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="52"/>
+      <c r="AH9" s="52"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="52"/>
       <c r="AK9" s="12"/>
       <c r="AL9" s="14"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="46"/>
-      <c r="T10" s="46"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="46"/>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46"/>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="46"/>
-      <c r="AB10" s="47"/>
+      <c r="B10" s="95"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="97"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="74"/>
+      <c r="S10" s="80"/>
+      <c r="T10" s="80"/>
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="80"/>
+      <c r="Z10" s="80"/>
+      <c r="AA10" s="80"/>
+      <c r="AB10" s="81"/>
       <c r="AC10" s="11"/>
-      <c r="AD10" s="38"/>
-      <c r="AE10" s="38"/>
-      <c r="AF10" s="38"/>
-      <c r="AG10" s="38"/>
-      <c r="AH10" s="38"/>
-      <c r="AI10" s="38"/>
-      <c r="AJ10" s="38"/>
+      <c r="AD10" s="52"/>
+      <c r="AE10" s="52"/>
+      <c r="AF10" s="52"/>
+      <c r="AG10" s="52"/>
+      <c r="AH10" s="52"/>
+      <c r="AI10" s="52"/>
+      <c r="AJ10" s="52"/>
       <c r="AK10" s="12"/>
       <c r="AL10" s="14"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="77"/>
-      <c r="I11" s="77"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="77"/>
-      <c r="L11" s="77"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="78"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="44"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="44"/>
-      <c r="V11" s="44"/>
-      <c r="W11" s="44"/>
-      <c r="X11" s="44"/>
-      <c r="Y11" s="44"/>
-      <c r="Z11" s="44"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="45"/>
-      <c r="AC11" s="32" t="s">
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="76"/>
+      <c r="S11" s="83"/>
+      <c r="T11" s="83"/>
+      <c r="U11" s="83"/>
+      <c r="V11" s="83"/>
+      <c r="W11" s="83"/>
+      <c r="X11" s="83"/>
+      <c r="Y11" s="83"/>
+      <c r="Z11" s="83"/>
+      <c r="AA11" s="83"/>
+      <c r="AB11" s="84"/>
+      <c r="AC11" s="70" t="s">
         <v>38</v>
       </c>
-      <c r="AD11" s="33"/>
-      <c r="AE11" s="33"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="33"/>
-      <c r="AH11" s="33"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="33"/>
-      <c r="AK11" s="33"/>
-      <c r="AL11" s="34"/>
+      <c r="AD11" s="71"/>
+      <c r="AE11" s="71"/>
+      <c r="AF11" s="71"/>
+      <c r="AG11" s="71"/>
+      <c r="AH11" s="71"/>
+      <c r="AI11" s="71"/>
+      <c r="AJ11" s="71"/>
+      <c r="AK11" s="71"/>
+      <c r="AL11" s="72"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1661,125 +1673,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="55" t="s">
+      <c r="B13" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="55"/>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-      <c r="S13" s="55"/>
-      <c r="T13" s="55"/>
-      <c r="U13" s="55"/>
-      <c r="V13" s="55"/>
-      <c r="W13" s="55"/>
-      <c r="X13" s="55"/>
-      <c r="Y13" s="55"/>
-      <c r="Z13" s="55"/>
-      <c r="AA13" s="55"/>
-      <c r="AB13" s="55"/>
-      <c r="AC13" s="55"/>
-      <c r="AD13" s="55"/>
-      <c r="AE13" s="55"/>
-      <c r="AF13" s="55"/>
-      <c r="AG13" s="55"/>
-      <c r="AH13" s="55"/>
-      <c r="AI13" s="55"/>
-      <c r="AJ13" s="55"/>
-      <c r="AK13" s="55"/>
-      <c r="AL13" s="55"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="59"/>
+      <c r="K13" s="59"/>
+      <c r="L13" s="59"/>
+      <c r="M13" s="59"/>
+      <c r="N13" s="59"/>
+      <c r="O13" s="59"/>
+      <c r="P13" s="59"/>
+      <c r="Q13" s="59"/>
+      <c r="R13" s="59"/>
+      <c r="S13" s="59"/>
+      <c r="T13" s="59"/>
+      <c r="U13" s="59"/>
+      <c r="V13" s="59"/>
+      <c r="W13" s="59"/>
+      <c r="X13" s="59"/>
+      <c r="Y13" s="59"/>
+      <c r="Z13" s="59"/>
+      <c r="AA13" s="59"/>
+      <c r="AB13" s="59"/>
+      <c r="AC13" s="59"/>
+      <c r="AD13" s="59"/>
+      <c r="AE13" s="59"/>
+      <c r="AF13" s="59"/>
+      <c r="AG13" s="59"/>
+      <c r="AH13" s="59"/>
+      <c r="AI13" s="59"/>
+      <c r="AJ13" s="59"/>
+      <c r="AK13" s="59"/>
+      <c r="AL13" s="59"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="55"/>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="55"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="55"/>
-      <c r="V14" s="55"/>
-      <c r="W14" s="55"/>
-      <c r="X14" s="55"/>
-      <c r="Y14" s="55"/>
-      <c r="Z14" s="55"/>
-      <c r="AA14" s="55"/>
-      <c r="AB14" s="55"/>
-      <c r="AC14" s="55"/>
-      <c r="AD14" s="55"/>
-      <c r="AE14" s="55"/>
-      <c r="AF14" s="55"/>
-      <c r="AG14" s="55"/>
-      <c r="AH14" s="55"/>
-      <c r="AI14" s="55"/>
-      <c r="AJ14" s="55"/>
-      <c r="AK14" s="55"/>
-      <c r="AL14" s="55"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+      <c r="J14" s="59"/>
+      <c r="K14" s="59"/>
+      <c r="L14" s="59"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="59"/>
+      <c r="O14" s="59"/>
+      <c r="P14" s="59"/>
+      <c r="Q14" s="59"/>
+      <c r="R14" s="59"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="59"/>
+      <c r="U14" s="59"/>
+      <c r="V14" s="59"/>
+      <c r="W14" s="59"/>
+      <c r="X14" s="59"/>
+      <c r="Y14" s="59"/>
+      <c r="Z14" s="59"/>
+      <c r="AA14" s="59"/>
+      <c r="AB14" s="59"/>
+      <c r="AC14" s="59"/>
+      <c r="AD14" s="59"/>
+      <c r="AE14" s="59"/>
+      <c r="AF14" s="59"/>
+      <c r="AG14" s="59"/>
+      <c r="AH14" s="59"/>
+      <c r="AI14" s="59"/>
+      <c r="AJ14" s="59"/>
+      <c r="AK14" s="59"/>
+      <c r="AL14" s="59"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="73"/>
-      <c r="L15" s="73"/>
-      <c r="M15" s="73"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="73"/>
-      <c r="U15" s="73"/>
-      <c r="V15" s="73"/>
-      <c r="W15" s="73"/>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="73"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="73"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="73"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="73"/>
-      <c r="AG15" s="73"/>
-      <c r="AH15" s="73"/>
-      <c r="AI15" s="73"/>
-      <c r="AJ15" s="73"/>
-      <c r="AK15" s="73"/>
-      <c r="AL15" s="73"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47"/>
+      <c r="P15" s="47"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
+      <c r="U15" s="47"/>
+      <c r="V15" s="47"/>
+      <c r="W15" s="47"/>
+      <c r="X15" s="47"/>
+      <c r="Y15" s="47"/>
+      <c r="Z15" s="47"/>
+      <c r="AA15" s="47"/>
+      <c r="AB15" s="47"/>
+      <c r="AC15" s="47"/>
+      <c r="AD15" s="47"/>
+      <c r="AE15" s="47"/>
+      <c r="AF15" s="47"/>
+      <c r="AG15" s="47"/>
+      <c r="AH15" s="47"/>
+      <c r="AI15" s="47"/>
+      <c r="AJ15" s="47"/>
+      <c r="AK15" s="47"/>
+      <c r="AL15" s="47"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1823,47 +1835,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="58" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="58"/>
-      <c r="Y17" s="58"/>
-      <c r="Z17" s="58"/>
-      <c r="AA17" s="58"/>
-      <c r="AB17" s="58"/>
-      <c r="AC17" s="58"/>
-      <c r="AD17" s="58"/>
-      <c r="AE17" s="58"/>
-      <c r="AF17" s="58"/>
-      <c r="AG17" s="58"/>
-      <c r="AH17" s="58"/>
-      <c r="AI17" s="58"/>
-      <c r="AJ17" s="58"/>
-      <c r="AK17" s="58"/>
-      <c r="AL17" s="58"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="60"/>
+      <c r="L17" s="60"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="60"/>
+      <c r="O17" s="60"/>
+      <c r="P17" s="60"/>
+      <c r="Q17" s="60"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="60"/>
+      <c r="T17" s="60"/>
+      <c r="U17" s="60"/>
+      <c r="V17" s="60"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="60"/>
+      <c r="Y17" s="60"/>
+      <c r="Z17" s="60"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
+      <c r="AF17" s="60"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="60"/>
+      <c r="AI17" s="60"/>
+      <c r="AJ17" s="60"/>
+      <c r="AK17" s="60"/>
+      <c r="AL17" s="60"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1907,47 +1919,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="58" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="58"/>
-      <c r="W19" s="58"/>
-      <c r="X19" s="58"/>
-      <c r="Y19" s="58"/>
-      <c r="Z19" s="58"/>
-      <c r="AA19" s="58"/>
-      <c r="AB19" s="58"/>
-      <c r="AC19" s="58"/>
-      <c r="AD19" s="58"/>
-      <c r="AE19" s="58"/>
-      <c r="AF19" s="58"/>
-      <c r="AG19" s="58"/>
-      <c r="AH19" s="58"/>
-      <c r="AI19" s="58"/>
-      <c r="AJ19" s="58"/>
-      <c r="AK19" s="58"/>
-      <c r="AL19" s="58"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="60"/>
+      <c r="N19" s="60"/>
+      <c r="O19" s="60"/>
+      <c r="P19" s="60"/>
+      <c r="Q19" s="60"/>
+      <c r="R19" s="60"/>
+      <c r="S19" s="60"/>
+      <c r="T19" s="60"/>
+      <c r="U19" s="60"/>
+      <c r="V19" s="60"/>
+      <c r="W19" s="60"/>
+      <c r="X19" s="60"/>
+      <c r="Y19" s="60"/>
+      <c r="Z19" s="60"/>
+      <c r="AA19" s="60"/>
+      <c r="AB19" s="60"/>
+      <c r="AC19" s="60"/>
+      <c r="AD19" s="60"/>
+      <c r="AE19" s="60"/>
+      <c r="AF19" s="60"/>
+      <c r="AG19" s="60"/>
+      <c r="AH19" s="60"/>
+      <c r="AI19" s="60"/>
+      <c r="AJ19" s="60"/>
+      <c r="AK19" s="60"/>
+      <c r="AL19" s="60"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -1991,160 +2003,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="67" t="s">
+      <c r="C21" s="30"/>
+      <c r="D21" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-      <c r="O21" s="68"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="68"/>
-      <c r="R21" s="68"/>
-      <c r="S21" s="67" t="s">
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="68"/>
-      <c r="U21" s="68"/>
-      <c r="V21" s="68"/>
-      <c r="W21" s="67" t="s">
+      <c r="T21" s="30"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="X21" s="68"/>
-      <c r="Y21" s="68"/>
-      <c r="Z21" s="79" t="s">
+      <c r="X21" s="30"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
-      <c r="AE21" s="81"/>
-      <c r="AF21" s="70" t="s">
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="AG21" s="68"/>
-      <c r="AH21" s="68"/>
-      <c r="AI21" s="68"/>
-      <c r="AJ21" s="68"/>
-      <c r="AK21" s="71"/>
+      <c r="AG21" s="30"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="30"/>
+      <c r="AJ21" s="30"/>
+      <c r="AK21" s="45"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="53">
+      <c r="B22" s="26">
         <v>1</v>
       </c>
-      <c r="C22" s="54"/>
-      <c r="D22" s="63" t="s">
+      <c r="C22" s="27"/>
+      <c r="D22" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="54"/>
-      <c r="F22" s="54"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="54"/>
-      <c r="J22" s="54"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="54"/>
-      <c r="M22" s="54"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="54"/>
-      <c r="P22" s="54"/>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="69">
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27"/>
+      <c r="K22" s="27"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="27"/>
+      <c r="N22" s="27"/>
+      <c r="O22" s="27"/>
+      <c r="P22" s="27"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="27"/>
+      <c r="S22" s="40">
         <v>1</v>
       </c>
-      <c r="T22" s="54"/>
-      <c r="U22" s="54"/>
-      <c r="V22" s="54"/>
-      <c r="W22" s="74" t="s">
+      <c r="T22" s="27"/>
+      <c r="U22" s="27"/>
+      <c r="V22" s="27"/>
+      <c r="W22" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="X22" s="54"/>
-      <c r="Y22" s="54"/>
-      <c r="Z22" s="82" t="s">
+      <c r="X22" s="27"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="AA22" s="83"/>
-      <c r="AB22" s="83"/>
-      <c r="AC22" s="83"/>
-      <c r="AD22" s="83"/>
-      <c r="AE22" s="84"/>
-      <c r="AF22" s="56" t="e">
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="36"/>
+      <c r="AF22" s="42" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="54"/>
-      <c r="AH22" s="54"/>
-      <c r="AI22" s="54"/>
-      <c r="AJ22" s="54"/>
-      <c r="AK22" s="57"/>
+      <c r="AG22" s="27"/>
+      <c r="AH22" s="27"/>
+      <c r="AI22" s="27"/>
+      <c r="AJ22" s="27"/>
+      <c r="AK22" s="43"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="53">
+      <c r="B23" s="26">
         <v>2</v>
       </c>
-      <c r="C23" s="54"/>
-      <c r="D23" s="63" t="s">
+      <c r="C23" s="27"/>
+      <c r="D23" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="54"/>
-      <c r="J23" s="54"/>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="69">
+      <c r="E23" s="27"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="27"/>
+      <c r="N23" s="27"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="27"/>
+      <c r="Q23" s="27"/>
+      <c r="R23" s="27"/>
+      <c r="S23" s="40">
         <v>1</v>
       </c>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54"/>
-      <c r="W23" s="74" t="s">
+      <c r="T23" s="27"/>
+      <c r="U23" s="27"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="X23" s="54"/>
-      <c r="Y23" s="54"/>
-      <c r="Z23" s="64" t="s">
+      <c r="X23" s="27"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="AA23" s="65"/>
-      <c r="AB23" s="65"/>
-      <c r="AC23" s="65"/>
-      <c r="AD23" s="65"/>
-      <c r="AE23" s="66"/>
-      <c r="AF23" s="56" t="e">
+      <c r="AA23" s="63"/>
+      <c r="AB23" s="63"/>
+      <c r="AC23" s="63"/>
+      <c r="AD23" s="63"/>
+      <c r="AE23" s="64"/>
+      <c r="AF23" s="42" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="54"/>
-      <c r="AH23" s="54"/>
-      <c r="AI23" s="54"/>
-      <c r="AJ23" s="54"/>
-      <c r="AK23" s="57"/>
+      <c r="AG23" s="27"/>
+      <c r="AH23" s="27"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="27"/>
+      <c r="AK23" s="43"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2221,15 +2233,15 @@
       <c r="AE25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="AF25" s="62" t="e">
+      <c r="AF25" s="50" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="28"/>
-      <c r="AH25" s="28"/>
-      <c r="AI25" s="28"/>
-      <c r="AJ25" s="28"/>
-      <c r="AK25" s="28"/>
+      <c r="AG25" s="51"/>
+      <c r="AH25" s="51"/>
+      <c r="AI25" s="51"/>
+      <c r="AJ25" s="51"/>
+      <c r="AK25" s="51"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2266,14 +2278,14 @@
       <c r="AE26" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="AF26" s="62" t="s">
+      <c r="AF26" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AG26" s="28"/>
-      <c r="AH26" s="28"/>
-      <c r="AI26" s="28"/>
-      <c r="AJ26" s="28"/>
-      <c r="AK26" s="28"/>
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51"/>
+      <c r="AK26" s="51"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2310,98 +2322,98 @@
       <c r="AE27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AF27" s="62" t="e">
+      <c r="AF27" s="50" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="28"/>
-      <c r="AH27" s="28"/>
-      <c r="AI27" s="28"/>
-      <c r="AJ27" s="28"/>
-      <c r="AK27" s="28"/>
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="51"/>
+      <c r="AK27" s="51"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="72"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="72"/>
-      <c r="Q28" s="72"/>
-      <c r="R28" s="72"/>
-      <c r="S28" s="72"/>
-      <c r="T28" s="72"/>
-      <c r="U28" s="72"/>
-      <c r="V28" s="72"/>
-      <c r="W28" s="72"/>
-      <c r="X28" s="72"/>
-      <c r="Y28" s="72"/>
-      <c r="Z28" s="72"/>
-      <c r="AA28" s="72"/>
-      <c r="AB28" s="72"/>
-      <c r="AC28" s="72"/>
-      <c r="AD28" s="72"/>
-      <c r="AE28" s="72"/>
-      <c r="AF28" s="72"/>
-      <c r="AG28" s="72"/>
-      <c r="AH28" s="72"/>
-      <c r="AI28" s="72"/>
-      <c r="AJ28" s="72"/>
-      <c r="AK28" s="72"/>
-      <c r="AL28" s="72"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+      <c r="R28" s="46"/>
+      <c r="S28" s="46"/>
+      <c r="T28" s="46"/>
+      <c r="U28" s="46"/>
+      <c r="V28" s="46"/>
+      <c r="W28" s="46"/>
+      <c r="X28" s="46"/>
+      <c r="Y28" s="46"/>
+      <c r="Z28" s="46"/>
+      <c r="AA28" s="46"/>
+      <c r="AB28" s="46"/>
+      <c r="AC28" s="46"/>
+      <c r="AD28" s="46"/>
+      <c r="AE28" s="46"/>
+      <c r="AF28" s="46"/>
+      <c r="AG28" s="46"/>
+      <c r="AH28" s="46"/>
+      <c r="AI28" s="46"/>
+      <c r="AJ28" s="46"/>
+      <c r="AK28" s="46"/>
+      <c r="AL28" s="46"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
-      <c r="B29" s="58" t="s">
+      <c r="B29" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="58"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="58"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="58"/>
-      <c r="AB29" s="58"/>
-      <c r="AC29" s="58"/>
-      <c r="AD29" s="58"/>
-      <c r="AE29" s="58"/>
-      <c r="AF29" s="58"/>
-      <c r="AG29" s="58"/>
-      <c r="AH29" s="58"/>
-      <c r="AI29" s="58"/>
-      <c r="AJ29" s="58"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="60"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="60"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+      <c r="R29" s="60"/>
+      <c r="S29" s="60"/>
+      <c r="T29" s="60"/>
+      <c r="U29" s="60"/>
+      <c r="V29" s="60"/>
+      <c r="W29" s="60"/>
+      <c r="X29" s="60"/>
+      <c r="Y29" s="60"/>
+      <c r="Z29" s="60"/>
+      <c r="AA29" s="60"/>
+      <c r="AB29" s="60"/>
+      <c r="AC29" s="60"/>
+      <c r="AD29" s="60"/>
+      <c r="AE29" s="60"/>
+      <c r="AF29" s="60"/>
+      <c r="AG29" s="60"/>
+      <c r="AH29" s="60"/>
+      <c r="AI29" s="60"/>
+      <c r="AJ29" s="60"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2546,23 +2558,23 @@
       <c r="P33" s="18"/>
       <c r="Q33" s="18"/>
       <c r="R33" s="16"/>
-      <c r="S33" s="52" t="s">
+      <c r="S33" s="58" t="s">
         <v>40</v>
       </c>
-      <c r="T33" s="52"/>
-      <c r="U33" s="52"/>
-      <c r="V33" s="52"/>
-      <c r="W33" s="52"/>
-      <c r="X33" s="52"/>
-      <c r="Y33" s="52"/>
-      <c r="Z33" s="52"/>
-      <c r="AA33" s="52"/>
-      <c r="AB33" s="52"/>
-      <c r="AC33" s="52"/>
-      <c r="AD33" s="52"/>
-      <c r="AE33" s="52"/>
-      <c r="AF33" s="52"/>
-      <c r="AG33" s="52"/>
+      <c r="T33" s="58"/>
+      <c r="U33" s="58"/>
+      <c r="V33" s="58"/>
+      <c r="W33" s="58"/>
+      <c r="X33" s="58"/>
+      <c r="Y33" s="58"/>
+      <c r="Z33" s="58"/>
+      <c r="AA33" s="58"/>
+      <c r="AB33" s="58"/>
+      <c r="AC33" s="58"/>
+      <c r="AD33" s="58"/>
+      <c r="AE33" s="58"/>
+      <c r="AF33" s="58"/>
+      <c r="AG33" s="58"/>
       <c r="AH33" s="16"/>
       <c r="AI33" s="16"/>
       <c r="AJ33" s="16"/>
@@ -2579,34 +2591,34 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
-      <c r="J34" s="60" t="s">
+      <c r="J34" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="61"/>
-      <c r="L34" s="61"/>
-      <c r="M34" s="61"/>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="61"/>
-      <c r="Q34" s="61"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="38"/>
+      <c r="Q34" s="38"/>
       <c r="R34" s="16"/>
-      <c r="S34" s="59" t="s">
+      <c r="S34" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="T34" s="59"/>
-      <c r="U34" s="59"/>
-      <c r="V34" s="59"/>
-      <c r="W34" s="59"/>
-      <c r="X34" s="59"/>
-      <c r="Y34" s="59"/>
-      <c r="Z34" s="59"/>
-      <c r="AA34" s="59"/>
-      <c r="AB34" s="59"/>
-      <c r="AC34" s="59"/>
-      <c r="AD34" s="59"/>
-      <c r="AE34" s="59"/>
-      <c r="AF34" s="59"/>
-      <c r="AG34" s="59"/>
+      <c r="T34" s="39"/>
+      <c r="U34" s="39"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="39"/>
+      <c r="Y34" s="39"/>
+      <c r="Z34" s="39"/>
+      <c r="AA34" s="39"/>
+      <c r="AB34" s="39"/>
+      <c r="AC34" s="39"/>
+      <c r="AD34" s="39"/>
+      <c r="AE34" s="39"/>
+      <c r="AF34" s="39"/>
+      <c r="AG34" s="39"/>
       <c r="AH34" s="16"/>
       <c r="AI34" s="16"/>
       <c r="AJ34" s="16"/>
@@ -2674,21 +2686,21 @@
       <c r="P36" s="18"/>
       <c r="Q36" s="18"/>
       <c r="R36" s="16"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-      <c r="AA36" s="52"/>
-      <c r="AB36" s="52"/>
-      <c r="AC36" s="52"/>
-      <c r="AD36" s="52"/>
-      <c r="AE36" s="52"/>
-      <c r="AF36" s="52"/>
-      <c r="AG36" s="52"/>
+      <c r="S36" s="58"/>
+      <c r="T36" s="58"/>
+      <c r="U36" s="58"/>
+      <c r="V36" s="58"/>
+      <c r="W36" s="58"/>
+      <c r="X36" s="58"/>
+      <c r="Y36" s="58"/>
+      <c r="Z36" s="58"/>
+      <c r="AA36" s="58"/>
+      <c r="AB36" s="58"/>
+      <c r="AC36" s="58"/>
+      <c r="AD36" s="58"/>
+      <c r="AE36" s="58"/>
+      <c r="AF36" s="58"/>
+      <c r="AG36" s="58"/>
       <c r="AH36" s="16"/>
       <c r="AI36" s="16"/>
       <c r="AJ36" s="16"/>
@@ -2705,34 +2717,34 @@
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
       <c r="I37" s="16"/>
-      <c r="J37" s="60" t="s">
+      <c r="J37" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="61"/>
-      <c r="L37" s="61"/>
-      <c r="M37" s="61"/>
-      <c r="N37" s="61"/>
-      <c r="O37" s="61"/>
-      <c r="P37" s="61"/>
-      <c r="Q37" s="61"/>
+      <c r="K37" s="38"/>
+      <c r="L37" s="38"/>
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="38"/>
+      <c r="P37" s="38"/>
+      <c r="Q37" s="38"/>
       <c r="R37" s="16"/>
-      <c r="S37" s="59" t="s">
+      <c r="S37" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="59"/>
-      <c r="U37" s="59"/>
-      <c r="V37" s="59"/>
-      <c r="W37" s="59"/>
-      <c r="X37" s="59"/>
-      <c r="Y37" s="59"/>
-      <c r="Z37" s="59"/>
-      <c r="AA37" s="59"/>
-      <c r="AB37" s="59"/>
-      <c r="AC37" s="59"/>
-      <c r="AD37" s="59"/>
-      <c r="AE37" s="59"/>
-      <c r="AF37" s="59"/>
-      <c r="AG37" s="59"/>
+      <c r="T37" s="39"/>
+      <c r="U37" s="39"/>
+      <c r="V37" s="39"/>
+      <c r="W37" s="39"/>
+      <c r="X37" s="39"/>
+      <c r="Y37" s="39"/>
+      <c r="Z37" s="39"/>
+      <c r="AA37" s="39"/>
+      <c r="AB37" s="39"/>
+      <c r="AC37" s="39"/>
+      <c r="AD37" s="39"/>
+      <c r="AE37" s="39"/>
+      <c r="AF37" s="39"/>
+      <c r="AG37" s="39"/>
       <c r="AH37" s="16"/>
       <c r="AI37" s="16"/>
       <c r="AJ37" s="16"/>
@@ -41143,12 +41155,34 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="S4:AB6"/>
+    <mergeCell ref="S2:AB3"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B2:N5"/>
+    <mergeCell ref="O2:R3"/>
+    <mergeCell ref="O4:R6"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:AL14"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="B29:AJ29"/>
+    <mergeCell ref="G19:AL19"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="J34:Q34"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="S33:AG33"/>
+    <mergeCell ref="D22:R22"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Z23:AE23"/>
+    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="W21:Y21"/>
     <mergeCell ref="J37:Q37"/>
     <mergeCell ref="S37:AG37"/>
     <mergeCell ref="S23:V23"/>
@@ -41165,34 +41199,12 @@
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B11:N11"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:AL14"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="B29:AJ29"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="S34:AG34"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="D22:R22"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="Z23:AE23"/>
-    <mergeCell ref="G17:AL17"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="B5:N6"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B8:N10"/>
-    <mergeCell ref="AC11:AL11"/>
-    <mergeCell ref="O7:R11"/>
-    <mergeCell ref="AD3:AJ10"/>
-    <mergeCell ref="O5:R6"/>
-    <mergeCell ref="S5:AB6"/>
-    <mergeCell ref="S7:AB11"/>
-    <mergeCell ref="O2:R4"/>
-    <mergeCell ref="S2:AB4"/>
-    <mergeCell ref="B2:N4"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="Z22:AE22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>

--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{190BC356-BA65-4DB9-B9BF-0A7EF4A41AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8A98C-3E68-476B-9E1A-31A72433F614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -633,127 +633,45 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -776,29 +694,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -806,38 +730,114 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1201,39 +1201,39 @@
     </row>
     <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="85" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="94"/>
-      <c r="S2" s="87" t="s">
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="59"/>
+      <c r="S2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="88"/>
-      <c r="W2" s="88"/>
-      <c r="X2" s="88"/>
-      <c r="Y2" s="88"/>
-      <c r="Z2" s="88"/>
-      <c r="AA2" s="88"/>
-      <c r="AB2" s="89"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="33"/>
+      <c r="AB2" s="34"/>
       <c r="AC2" s="22"/>
       <c r="AD2" s="22"/>
       <c r="AE2" s="22"/>
@@ -1247,169 +1247,169 @@
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="69"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
-      <c r="Z3" s="80"/>
-      <c r="AA3" s="80"/>
-      <c r="AB3" s="81"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="60"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="28"/>
       <c r="AC3" s="20"/>
-      <c r="AD3" s="52" t="s">
+      <c r="AD3" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="52"/>
-      <c r="AF3" s="52"/>
-      <c r="AG3" s="52"/>
-      <c r="AH3" s="52"/>
-      <c r="AI3" s="52"/>
-      <c r="AJ3" s="52"/>
+      <c r="AE3" s="47"/>
+      <c r="AF3" s="47"/>
+      <c r="AG3" s="47"/>
+      <c r="AH3" s="47"/>
+      <c r="AI3" s="47"/>
+      <c r="AJ3" s="47"/>
       <c r="AK3" s="20"/>
       <c r="AL3" s="21"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="69"/>
-      <c r="O4" s="77" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="55"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="79" t="s">
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="80"/>
-      <c r="U4" s="80"/>
-      <c r="V4" s="80"/>
-      <c r="W4" s="80"/>
-      <c r="X4" s="80"/>
-      <c r="Y4" s="80"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="81"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27"/>
+      <c r="AA4" s="27"/>
+      <c r="AB4" s="28"/>
       <c r="AC4" s="9"/>
-      <c r="AD4" s="52"/>
-      <c r="AE4" s="52"/>
-      <c r="AF4" s="52"/>
-      <c r="AG4" s="52"/>
-      <c r="AH4" s="52"/>
-      <c r="AI4" s="52"/>
-      <c r="AJ4" s="52"/>
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="47"/>
+      <c r="AG4" s="47"/>
+      <c r="AH4" s="47"/>
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
       <c r="AK4" s="9"/>
       <c r="AL4" s="10"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="69"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="73"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="80"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="80"/>
-      <c r="W5" s="80"/>
-      <c r="X5" s="80"/>
-      <c r="Y5" s="80"/>
-      <c r="Z5" s="80"/>
-      <c r="AA5" s="80"/>
-      <c r="AB5" s="81"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
+      <c r="M5" s="55"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="60"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="44"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="28"/>
       <c r="AC5" s="12"/>
-      <c r="AD5" s="52"/>
-      <c r="AE5" s="52"/>
-      <c r="AF5" s="52"/>
-      <c r="AG5" s="52"/>
-      <c r="AH5" s="52"/>
-      <c r="AI5" s="52"/>
-      <c r="AJ5" s="52"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
       <c r="AK5" s="12"/>
       <c r="AL5" s="13"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="65" t="s">
+      <c r="B6" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
-      <c r="L6" s="66"/>
-      <c r="M6" s="66"/>
-      <c r="N6" s="92"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="75"/>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="82"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
-      <c r="Y6" s="83"/>
-      <c r="Z6" s="83"/>
-      <c r="AA6" s="83"/>
-      <c r="AB6" s="84"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="61"/>
+      <c r="P6" s="45"/>
+      <c r="Q6" s="45"/>
+      <c r="R6" s="46"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="30"/>
+      <c r="X6" s="30"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="30"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="31"/>
       <c r="AC6" s="12"/>
-      <c r="AD6" s="52"/>
-      <c r="AE6" s="52"/>
-      <c r="AF6" s="52"/>
-      <c r="AG6" s="52"/>
-      <c r="AH6" s="52"/>
-      <c r="AI6" s="52"/>
-      <c r="AJ6" s="52"/>
+      <c r="AD6" s="47"/>
+      <c r="AE6" s="47"/>
+      <c r="AF6" s="47"/>
+      <c r="AG6" s="47"/>
+      <c r="AH6" s="47"/>
+      <c r="AI6" s="47"/>
+      <c r="AJ6" s="47"/>
       <c r="AK6" s="12"/>
       <c r="AL6" s="14"/>
     </row>
@@ -1419,217 +1419,217 @@
         <v>5</v>
       </c>
       <c r="C7" s="25"/>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="41" t="s">
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="41"/>
-      <c r="K7" s="56" t="s">
+      <c r="J7" s="80"/>
+      <c r="K7" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="73" t="s">
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
+      <c r="N7" s="91"/>
+      <c r="O7" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="73"/>
-      <c r="R7" s="74"/>
-      <c r="S7" s="80" t="s">
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="44"/>
+      <c r="S7" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="T7" s="80"/>
-      <c r="U7" s="80"/>
-      <c r="V7" s="80"/>
-      <c r="W7" s="80"/>
-      <c r="X7" s="80"/>
-      <c r="Y7" s="80"/>
-      <c r="Z7" s="80"/>
-      <c r="AA7" s="80"/>
-      <c r="AB7" s="81"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="28"/>
       <c r="AC7" s="11"/>
-      <c r="AD7" s="52"/>
-      <c r="AE7" s="52"/>
-      <c r="AF7" s="52"/>
-      <c r="AG7" s="52"/>
-      <c r="AH7" s="52"/>
-      <c r="AI7" s="52"/>
-      <c r="AJ7" s="52"/>
+      <c r="AD7" s="47"/>
+      <c r="AE7" s="47"/>
+      <c r="AF7" s="47"/>
+      <c r="AG7" s="47"/>
+      <c r="AH7" s="47"/>
+      <c r="AI7" s="47"/>
+      <c r="AJ7" s="47"/>
       <c r="AK7" s="12"/>
       <c r="AL7" s="14"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="96"/>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="97"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
-      <c r="Q8" s="73"/>
-      <c r="R8" s="74"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="80"/>
-      <c r="U8" s="80"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="80"/>
-      <c r="X8" s="80"/>
-      <c r="Y8" s="80"/>
-      <c r="Z8" s="80"/>
-      <c r="AA8" s="80"/>
-      <c r="AB8" s="81"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="44"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="27"/>
+      <c r="U8" s="27"/>
+      <c r="V8" s="27"/>
+      <c r="W8" s="27"/>
+      <c r="X8" s="27"/>
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27"/>
+      <c r="AB8" s="28"/>
       <c r="AC8" s="11"/>
-      <c r="AD8" s="52"/>
-      <c r="AE8" s="52"/>
-      <c r="AF8" s="52"/>
-      <c r="AG8" s="52"/>
-      <c r="AH8" s="52"/>
-      <c r="AI8" s="52"/>
-      <c r="AJ8" s="52"/>
+      <c r="AD8" s="47"/>
+      <c r="AE8" s="47"/>
+      <c r="AF8" s="47"/>
+      <c r="AG8" s="47"/>
+      <c r="AH8" s="47"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
       <c r="AK8" s="12"/>
       <c r="AL8" s="14"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="95"/>
-      <c r="C9" s="96"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="96"/>
-      <c r="F9" s="96"/>
-      <c r="G9" s="96"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="96"/>
-      <c r="J9" s="96"/>
-      <c r="K9" s="96"/>
-      <c r="L9" s="96"/>
-      <c r="M9" s="96"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="74"/>
-      <c r="S9" s="80"/>
-      <c r="T9" s="80"/>
-      <c r="U9" s="80"/>
-      <c r="V9" s="80"/>
-      <c r="W9" s="80"/>
-      <c r="X9" s="80"/>
-      <c r="Y9" s="80"/>
-      <c r="Z9" s="80"/>
-      <c r="AA9" s="80"/>
-      <c r="AB9" s="81"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="44"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="27"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="27"/>
+      <c r="W9" s="27"/>
+      <c r="X9" s="27"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27"/>
+      <c r="AB9" s="28"/>
       <c r="AC9" s="11"/>
-      <c r="AD9" s="52"/>
-      <c r="AE9" s="52"/>
-      <c r="AF9" s="52"/>
-      <c r="AG9" s="52"/>
-      <c r="AH9" s="52"/>
-      <c r="AI9" s="52"/>
-      <c r="AJ9" s="52"/>
+      <c r="AD9" s="47"/>
+      <c r="AE9" s="47"/>
+      <c r="AF9" s="47"/>
+      <c r="AG9" s="47"/>
+      <c r="AH9" s="47"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
       <c r="AK9" s="12"/>
       <c r="AL9" s="14"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="95"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="96"/>
-      <c r="H10" s="96"/>
-      <c r="I10" s="96"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="97"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="74"/>
-      <c r="S10" s="80"/>
-      <c r="T10" s="80"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="80"/>
-      <c r="W10" s="80"/>
-      <c r="X10" s="80"/>
-      <c r="Y10" s="80"/>
-      <c r="Z10" s="80"/>
-      <c r="AA10" s="80"/>
-      <c r="AB10" s="81"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="27"/>
+      <c r="T10" s="27"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27"/>
+      <c r="AB10" s="28"/>
       <c r="AC10" s="11"/>
-      <c r="AD10" s="52"/>
-      <c r="AE10" s="52"/>
-      <c r="AF10" s="52"/>
-      <c r="AG10" s="52"/>
-      <c r="AH10" s="52"/>
-      <c r="AI10" s="52"/>
-      <c r="AJ10" s="52"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
+      <c r="AJ10" s="47"/>
       <c r="AK10" s="12"/>
       <c r="AL10" s="14"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="55"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
-      <c r="Q11" s="75"/>
-      <c r="R11" s="76"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
-      <c r="Y11" s="83"/>
-      <c r="Z11" s="83"/>
-      <c r="AA11" s="83"/>
-      <c r="AB11" s="84"/>
-      <c r="AC11" s="70" t="s">
+      <c r="C11" s="88"/>
+      <c r="D11" s="88"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="88"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="88"/>
+      <c r="L11" s="88"/>
+      <c r="M11" s="88"/>
+      <c r="N11" s="89"/>
+      <c r="O11" s="45"/>
+      <c r="P11" s="45"/>
+      <c r="Q11" s="45"/>
+      <c r="R11" s="46"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="30"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="AD11" s="71"/>
-      <c r="AE11" s="71"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="71"/>
-      <c r="AH11" s="71"/>
-      <c r="AI11" s="71"/>
-      <c r="AJ11" s="71"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="72"/>
+      <c r="AD11" s="41"/>
+      <c r="AE11" s="41"/>
+      <c r="AF11" s="41"/>
+      <c r="AG11" s="41"/>
+      <c r="AH11" s="41"/>
+      <c r="AI11" s="41"/>
+      <c r="AJ11" s="41"/>
+      <c r="AK11" s="41"/>
+      <c r="AL11" s="42"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1673,125 +1673,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="59"/>
-      <c r="K13" s="59"/>
-      <c r="L13" s="59"/>
-      <c r="M13" s="59"/>
-      <c r="N13" s="59"/>
-      <c r="O13" s="59"/>
-      <c r="P13" s="59"/>
-      <c r="Q13" s="59"/>
-      <c r="R13" s="59"/>
-      <c r="S13" s="59"/>
-      <c r="T13" s="59"/>
-      <c r="U13" s="59"/>
-      <c r="V13" s="59"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59"/>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59"/>
-      <c r="AL13" s="59"/>
+      <c r="C13" s="65"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="65"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="65"/>
+      <c r="M13" s="65"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="65"/>
+      <c r="P13" s="65"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="65"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="65"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="65"/>
+      <c r="Z13" s="65"/>
+      <c r="AA13" s="65"/>
+      <c r="AB13" s="65"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="65"/>
+      <c r="AE13" s="65"/>
+      <c r="AF13" s="65"/>
+      <c r="AG13" s="65"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="65"/>
+      <c r="AJ13" s="65"/>
+      <c r="AK13" s="65"/>
+      <c r="AL13" s="65"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="59"/>
-      <c r="C14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="59"/>
-      <c r="N14" s="59"/>
-      <c r="O14" s="59"/>
-      <c r="P14" s="59"/>
-      <c r="Q14" s="59"/>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="59"/>
-      <c r="U14" s="59"/>
-      <c r="V14" s="59"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="59"/>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="59"/>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="59"/>
-      <c r="AF14" s="59"/>
-      <c r="AG14" s="59"/>
-      <c r="AH14" s="59"/>
-      <c r="AI14" s="59"/>
-      <c r="AJ14" s="59"/>
-      <c r="AK14" s="59"/>
-      <c r="AL14" s="59"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="65"/>
+      <c r="M14" s="65"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="65"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="65"/>
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="65"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="65"/>
+      <c r="AE14" s="65"/>
+      <c r="AF14" s="65"/>
+      <c r="AG14" s="65"/>
+      <c r="AH14" s="65"/>
+      <c r="AI14" s="65"/>
+      <c r="AJ14" s="65"/>
+      <c r="AK14" s="65"/>
+      <c r="AL14" s="65"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="47"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="47"/>
-      <c r="AF15" s="47"/>
-      <c r="AG15" s="47"/>
-      <c r="AH15" s="47"/>
-      <c r="AI15" s="47"/>
-      <c r="AJ15" s="47"/>
-      <c r="AK15" s="47"/>
-      <c r="AL15" s="47"/>
+      <c r="B15" s="84"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="84"/>
+      <c r="O15" s="84"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="84"/>
+      <c r="AE15" s="84"/>
+      <c r="AF15" s="84"/>
+      <c r="AG15" s="84"/>
+      <c r="AH15" s="84"/>
+      <c r="AI15" s="84"/>
+      <c r="AJ15" s="84"/>
+      <c r="AK15" s="84"/>
+      <c r="AL15" s="84"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1835,47 +1835,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="61" t="s">
+      <c r="B17" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="60" t="s">
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="60"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="60"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="60"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="60"/>
-      <c r="U17" s="60"/>
-      <c r="V17" s="60"/>
-      <c r="W17" s="60"/>
-      <c r="X17" s="60"/>
-      <c r="Y17" s="60"/>
-      <c r="Z17" s="60"/>
-      <c r="AA17" s="60"/>
-      <c r="AB17" s="60"/>
-      <c r="AC17" s="60"/>
-      <c r="AD17" s="60"/>
-      <c r="AE17" s="60"/>
-      <c r="AF17" s="60"/>
-      <c r="AG17" s="60"/>
-      <c r="AH17" s="60"/>
-      <c r="AI17" s="60"/>
-      <c r="AJ17" s="60"/>
-      <c r="AK17" s="60"/>
-      <c r="AL17" s="60"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
+      <c r="J17" s="68"/>
+      <c r="K17" s="68"/>
+      <c r="L17" s="68"/>
+      <c r="M17" s="68"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="68"/>
+      <c r="Q17" s="68"/>
+      <c r="R17" s="68"/>
+      <c r="S17" s="68"/>
+      <c r="T17" s="68"/>
+      <c r="U17" s="68"/>
+      <c r="V17" s="68"/>
+      <c r="W17" s="68"/>
+      <c r="X17" s="68"/>
+      <c r="Y17" s="68"/>
+      <c r="Z17" s="68"/>
+      <c r="AA17" s="68"/>
+      <c r="AB17" s="68"/>
+      <c r="AC17" s="68"/>
+      <c r="AD17" s="68"/>
+      <c r="AE17" s="68"/>
+      <c r="AF17" s="68"/>
+      <c r="AG17" s="68"/>
+      <c r="AH17" s="68"/>
+      <c r="AI17" s="68"/>
+      <c r="AJ17" s="68"/>
+      <c r="AK17" s="68"/>
+      <c r="AL17" s="68"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1919,47 +1919,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="60" t="s">
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="60"/>
-      <c r="I19" s="60"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="60"/>
-      <c r="O19" s="60"/>
-      <c r="P19" s="60"/>
-      <c r="Q19" s="60"/>
-      <c r="R19" s="60"/>
-      <c r="S19" s="60"/>
-      <c r="T19" s="60"/>
-      <c r="U19" s="60"/>
-      <c r="V19" s="60"/>
-      <c r="W19" s="60"/>
-      <c r="X19" s="60"/>
-      <c r="Y19" s="60"/>
-      <c r="Z19" s="60"/>
-      <c r="AA19" s="60"/>
-      <c r="AB19" s="60"/>
-      <c r="AC19" s="60"/>
-      <c r="AD19" s="60"/>
-      <c r="AE19" s="60"/>
-      <c r="AF19" s="60"/>
-      <c r="AG19" s="60"/>
-      <c r="AH19" s="60"/>
-      <c r="AI19" s="60"/>
-      <c r="AJ19" s="60"/>
-      <c r="AK19" s="60"/>
-      <c r="AL19" s="60"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="68"/>
+      <c r="P19" s="68"/>
+      <c r="Q19" s="68"/>
+      <c r="R19" s="68"/>
+      <c r="S19" s="68"/>
+      <c r="T19" s="68"/>
+      <c r="U19" s="68"/>
+      <c r="V19" s="68"/>
+      <c r="W19" s="68"/>
+      <c r="X19" s="68"/>
+      <c r="Y19" s="68"/>
+      <c r="Z19" s="68"/>
+      <c r="AA19" s="68"/>
+      <c r="AB19" s="68"/>
+      <c r="AC19" s="68"/>
+      <c r="AD19" s="68"/>
+      <c r="AE19" s="68"/>
+      <c r="AF19" s="68"/>
+      <c r="AG19" s="68"/>
+      <c r="AH19" s="68"/>
+      <c r="AI19" s="68"/>
+      <c r="AJ19" s="68"/>
+      <c r="AK19" s="68"/>
+      <c r="AL19" s="68"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2003,160 +2003,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="29" t="s">
+      <c r="C21" s="78"/>
+      <c r="D21" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
-      <c r="L21" s="30"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="30"/>
-      <c r="P21" s="30"/>
-      <c r="Q21" s="30"/>
-      <c r="R21" s="30"/>
-      <c r="S21" s="29" t="s">
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="78"/>
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="30"/>
-      <c r="U21" s="30"/>
-      <c r="V21" s="30"/>
-      <c r="W21" s="29" t="s">
+      <c r="T21" s="78"/>
+      <c r="U21" s="78"/>
+      <c r="V21" s="78"/>
+      <c r="W21" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="X21" s="30"/>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="31" t="s">
+      <c r="X21" s="78"/>
+      <c r="Y21" s="78"/>
+      <c r="Z21" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="AA21" s="32"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="32"/>
-      <c r="AD21" s="32"/>
-      <c r="AE21" s="33"/>
-      <c r="AF21" s="44" t="s">
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="93"/>
+      <c r="AC21" s="93"/>
+      <c r="AD21" s="93"/>
+      <c r="AE21" s="94"/>
+      <c r="AF21" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="AG21" s="30"/>
-      <c r="AH21" s="30"/>
-      <c r="AI21" s="30"/>
-      <c r="AJ21" s="30"/>
-      <c r="AK21" s="45"/>
+      <c r="AG21" s="78"/>
+      <c r="AH21" s="78"/>
+      <c r="AI21" s="78"/>
+      <c r="AJ21" s="78"/>
+      <c r="AK21" s="82"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="26">
+      <c r="B22" s="63">
         <v>1</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="48" t="s">
+      <c r="C22" s="64"/>
+      <c r="D22" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="40">
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64"/>
+      <c r="R22" s="64"/>
+      <c r="S22" s="79">
         <v>1</v>
       </c>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="28" t="s">
+      <c r="T22" s="64"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="34" t="s">
+      <c r="X22" s="64"/>
+      <c r="Y22" s="64"/>
+      <c r="Z22" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="AA22" s="35"/>
-      <c r="AB22" s="35"/>
-      <c r="AC22" s="35"/>
-      <c r="AD22" s="35"/>
-      <c r="AE22" s="36"/>
-      <c r="AF22" s="42" t="e">
+      <c r="AA22" s="96"/>
+      <c r="AB22" s="96"/>
+      <c r="AC22" s="96"/>
+      <c r="AD22" s="96"/>
+      <c r="AE22" s="97"/>
+      <c r="AF22" s="66" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="27"/>
-      <c r="AH22" s="27"/>
-      <c r="AI22" s="27"/>
-      <c r="AJ22" s="27"/>
-      <c r="AK22" s="43"/>
+      <c r="AG22" s="64"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="67"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="26">
+      <c r="B23" s="63">
         <v>2</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="48" t="s">
+      <c r="C23" s="64"/>
+      <c r="D23" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="40">
+      <c r="E23" s="64"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="64"/>
+      <c r="I23" s="64"/>
+      <c r="J23" s="64"/>
+      <c r="K23" s="64"/>
+      <c r="L23" s="64"/>
+      <c r="M23" s="64"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="64"/>
+      <c r="P23" s="64"/>
+      <c r="Q23" s="64"/>
+      <c r="R23" s="64"/>
+      <c r="S23" s="79">
         <v>1</v>
       </c>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="28" t="s">
+      <c r="T23" s="64"/>
+      <c r="U23" s="64"/>
+      <c r="V23" s="64"/>
+      <c r="W23" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="62" t="s">
+      <c r="X23" s="64"/>
+      <c r="Y23" s="64"/>
+      <c r="Z23" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="AA23" s="63"/>
-      <c r="AB23" s="63"/>
-      <c r="AC23" s="63"/>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="64"/>
-      <c r="AF23" s="42" t="e">
+      <c r="AA23" s="75"/>
+      <c r="AB23" s="75"/>
+      <c r="AC23" s="75"/>
+      <c r="AD23" s="75"/>
+      <c r="AE23" s="76"/>
+      <c r="AF23" s="66" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
-      <c r="AI23" s="27"/>
-      <c r="AJ23" s="27"/>
-      <c r="AK23" s="43"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="67"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2233,15 +2233,15 @@
       <c r="AE25" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="AF25" s="50" t="e">
+      <c r="AF25" s="72" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="51"/>
-      <c r="AH25" s="51"/>
-      <c r="AI25" s="51"/>
-      <c r="AJ25" s="51"/>
-      <c r="AK25" s="51"/>
+      <c r="AG25" s="36"/>
+      <c r="AH25" s="36"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="36"/>
+      <c r="AK25" s="36"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2278,14 +2278,14 @@
       <c r="AE26" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="AF26" s="50" t="s">
+      <c r="AF26" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="AG26" s="51"/>
-      <c r="AH26" s="51"/>
-      <c r="AI26" s="51"/>
-      <c r="AJ26" s="51"/>
-      <c r="AK26" s="51"/>
+      <c r="AG26" s="36"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2322,98 +2322,98 @@
       <c r="AE27" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="AF27" s="50" t="e">
+      <c r="AF27" s="72" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="51"/>
-      <c r="AH27" s="51"/>
-      <c r="AI27" s="51"/>
-      <c r="AJ27" s="51"/>
-      <c r="AK27" s="51"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="46"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="46"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="46"/>
-      <c r="S28" s="46"/>
-      <c r="T28" s="46"/>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46"/>
-      <c r="X28" s="46"/>
-      <c r="Y28" s="46"/>
-      <c r="Z28" s="46"/>
-      <c r="AA28" s="46"/>
-      <c r="AB28" s="46"/>
-      <c r="AC28" s="46"/>
-      <c r="AD28" s="46"/>
-      <c r="AE28" s="46"/>
-      <c r="AF28" s="46"/>
-      <c r="AG28" s="46"/>
-      <c r="AH28" s="46"/>
-      <c r="AI28" s="46"/>
-      <c r="AJ28" s="46"/>
-      <c r="AK28" s="46"/>
-      <c r="AL28" s="46"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="83"/>
+      <c r="G28" s="83"/>
+      <c r="H28" s="83"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="83"/>
+      <c r="K28" s="83"/>
+      <c r="L28" s="83"/>
+      <c r="M28" s="83"/>
+      <c r="N28" s="83"/>
+      <c r="O28" s="83"/>
+      <c r="P28" s="83"/>
+      <c r="Q28" s="83"/>
+      <c r="R28" s="83"/>
+      <c r="S28" s="83"/>
+      <c r="T28" s="83"/>
+      <c r="U28" s="83"/>
+      <c r="V28" s="83"/>
+      <c r="W28" s="83"/>
+      <c r="X28" s="83"/>
+      <c r="Y28" s="83"/>
+      <c r="Z28" s="83"/>
+      <c r="AA28" s="83"/>
+      <c r="AB28" s="83"/>
+      <c r="AC28" s="83"/>
+      <c r="AD28" s="83"/>
+      <c r="AE28" s="83"/>
+      <c r="AF28" s="83"/>
+      <c r="AG28" s="83"/>
+      <c r="AH28" s="83"/>
+      <c r="AI28" s="83"/>
+      <c r="AJ28" s="83"/>
+      <c r="AK28" s="83"/>
+      <c r="AL28" s="83"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="60"/>
-      <c r="J29" s="60"/>
-      <c r="K29" s="60"/>
-      <c r="L29" s="60"/>
-      <c r="M29" s="60"/>
-      <c r="N29" s="60"/>
-      <c r="O29" s="60"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="60"/>
-      <c r="T29" s="60"/>
-      <c r="U29" s="60"/>
-      <c r="V29" s="60"/>
-      <c r="W29" s="60"/>
-      <c r="X29" s="60"/>
-      <c r="Y29" s="60"/>
-      <c r="Z29" s="60"/>
-      <c r="AA29" s="60"/>
-      <c r="AB29" s="60"/>
-      <c r="AC29" s="60"/>
-      <c r="AD29" s="60"/>
-      <c r="AE29" s="60"/>
-      <c r="AF29" s="60"/>
-      <c r="AG29" s="60"/>
-      <c r="AH29" s="60"/>
-      <c r="AI29" s="60"/>
-      <c r="AJ29" s="60"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
+      <c r="Y29" s="68"/>
+      <c r="Z29" s="68"/>
+      <c r="AA29" s="68"/>
+      <c r="AB29" s="68"/>
+      <c r="AC29" s="68"/>
+      <c r="AD29" s="68"/>
+      <c r="AE29" s="68"/>
+      <c r="AF29" s="68"/>
+      <c r="AG29" s="68"/>
+      <c r="AH29" s="68"/>
+      <c r="AI29" s="68"/>
+      <c r="AJ29" s="68"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2558,23 +2558,23 @@
       <c r="P33" s="18"/>
       <c r="Q33" s="18"/>
       <c r="R33" s="16"/>
-      <c r="S33" s="58" t="s">
+      <c r="S33" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="T33" s="58"/>
-      <c r="U33" s="58"/>
-      <c r="V33" s="58"/>
-      <c r="W33" s="58"/>
-      <c r="X33" s="58"/>
-      <c r="Y33" s="58"/>
-      <c r="Z33" s="58"/>
-      <c r="AA33" s="58"/>
-      <c r="AB33" s="58"/>
-      <c r="AC33" s="58"/>
-      <c r="AD33" s="58"/>
-      <c r="AE33" s="58"/>
-      <c r="AF33" s="58"/>
-      <c r="AG33" s="58"/>
+      <c r="T33" s="62"/>
+      <c r="U33" s="62"/>
+      <c r="V33" s="62"/>
+      <c r="W33" s="62"/>
+      <c r="X33" s="62"/>
+      <c r="Y33" s="62"/>
+      <c r="Z33" s="62"/>
+      <c r="AA33" s="62"/>
+      <c r="AB33" s="62"/>
+      <c r="AC33" s="62"/>
+      <c r="AD33" s="62"/>
+      <c r="AE33" s="62"/>
+      <c r="AF33" s="62"/>
+      <c r="AG33" s="62"/>
       <c r="AH33" s="16"/>
       <c r="AI33" s="16"/>
       <c r="AJ33" s="16"/>
@@ -2591,34 +2591,34 @@
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
-      <c r="J34" s="37" t="s">
+      <c r="J34" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
       <c r="R34" s="16"/>
-      <c r="S34" s="39" t="s">
+      <c r="S34" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="T34" s="39"/>
-      <c r="U34" s="39"/>
-      <c r="V34" s="39"/>
-      <c r="W34" s="39"/>
-      <c r="X34" s="39"/>
-      <c r="Y34" s="39"/>
-      <c r="Z34" s="39"/>
-      <c r="AA34" s="39"/>
-      <c r="AB34" s="39"/>
-      <c r="AC34" s="39"/>
-      <c r="AD34" s="39"/>
-      <c r="AE34" s="39"/>
-      <c r="AF34" s="39"/>
-      <c r="AG34" s="39"/>
+      <c r="T34" s="69"/>
+      <c r="U34" s="69"/>
+      <c r="V34" s="69"/>
+      <c r="W34" s="69"/>
+      <c r="X34" s="69"/>
+      <c r="Y34" s="69"/>
+      <c r="Z34" s="69"/>
+      <c r="AA34" s="69"/>
+      <c r="AB34" s="69"/>
+      <c r="AC34" s="69"/>
+      <c r="AD34" s="69"/>
+      <c r="AE34" s="69"/>
+      <c r="AF34" s="69"/>
+      <c r="AG34" s="69"/>
       <c r="AH34" s="16"/>
       <c r="AI34" s="16"/>
       <c r="AJ34" s="16"/>
@@ -2686,21 +2686,21 @@
       <c r="P36" s="18"/>
       <c r="Q36" s="18"/>
       <c r="R36" s="16"/>
-      <c r="S36" s="58"/>
-      <c r="T36" s="58"/>
-      <c r="U36" s="58"/>
-      <c r="V36" s="58"/>
-      <c r="W36" s="58"/>
-      <c r="X36" s="58"/>
-      <c r="Y36" s="58"/>
-      <c r="Z36" s="58"/>
-      <c r="AA36" s="58"/>
-      <c r="AB36" s="58"/>
-      <c r="AC36" s="58"/>
-      <c r="AD36" s="58"/>
-      <c r="AE36" s="58"/>
-      <c r="AF36" s="58"/>
-      <c r="AG36" s="58"/>
+      <c r="S36" s="62"/>
+      <c r="T36" s="62"/>
+      <c r="U36" s="62"/>
+      <c r="V36" s="62"/>
+      <c r="W36" s="62"/>
+      <c r="X36" s="62"/>
+      <c r="Y36" s="62"/>
+      <c r="Z36" s="62"/>
+      <c r="AA36" s="62"/>
+      <c r="AB36" s="62"/>
+      <c r="AC36" s="62"/>
+      <c r="AD36" s="62"/>
+      <c r="AE36" s="62"/>
+      <c r="AF36" s="62"/>
+      <c r="AG36" s="62"/>
       <c r="AH36" s="16"/>
       <c r="AI36" s="16"/>
       <c r="AJ36" s="16"/>
@@ -2717,34 +2717,34 @@
       <c r="G37" s="16"/>
       <c r="H37" s="16"/>
       <c r="I37" s="16"/>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="38"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71"/>
       <c r="R37" s="16"/>
-      <c r="S37" s="39" t="s">
+      <c r="S37" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="39"/>
-      <c r="U37" s="39"/>
-      <c r="V37" s="39"/>
-      <c r="W37" s="39"/>
-      <c r="X37" s="39"/>
-      <c r="Y37" s="39"/>
-      <c r="Z37" s="39"/>
-      <c r="AA37" s="39"/>
-      <c r="AB37" s="39"/>
-      <c r="AC37" s="39"/>
-      <c r="AD37" s="39"/>
-      <c r="AE37" s="39"/>
-      <c r="AF37" s="39"/>
-      <c r="AG37" s="39"/>
+      <c r="T37" s="69"/>
+      <c r="U37" s="69"/>
+      <c r="V37" s="69"/>
+      <c r="W37" s="69"/>
+      <c r="X37" s="69"/>
+      <c r="Y37" s="69"/>
+      <c r="Z37" s="69"/>
+      <c r="AA37" s="69"/>
+      <c r="AB37" s="69"/>
+      <c r="AC37" s="69"/>
+      <c r="AD37" s="69"/>
+      <c r="AE37" s="69"/>
+      <c r="AF37" s="69"/>
+      <c r="AG37" s="69"/>
       <c r="AH37" s="16"/>
       <c r="AI37" s="16"/>
       <c r="AJ37" s="16"/>
@@ -41155,18 +41155,28 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="S4:AB6"/>
-    <mergeCell ref="S2:AB3"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B8:N10"/>
-    <mergeCell ref="AC11:AL11"/>
-    <mergeCell ref="O7:R11"/>
-    <mergeCell ref="AD3:AJ10"/>
-    <mergeCell ref="S7:AB11"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="B2:N5"/>
-    <mergeCell ref="O2:R3"/>
-    <mergeCell ref="O4:R6"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="J37:Q37"/>
+    <mergeCell ref="S37:AG37"/>
+    <mergeCell ref="S23:V23"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="S22:V22"/>
+    <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="B28:AL28"/>
+    <mergeCell ref="B15:AL15"/>
+    <mergeCell ref="D23:R23"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="AF26:AK26"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B11:N11"/>
+    <mergeCell ref="K7:N7"/>
     <mergeCell ref="S36:AG36"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:AL14"/>
@@ -41183,31 +41193,21 @@
     <mergeCell ref="Z23:AE23"/>
     <mergeCell ref="G17:AL17"/>
     <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="J37:Q37"/>
-    <mergeCell ref="S37:AG37"/>
-    <mergeCell ref="S23:V23"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="S22:V22"/>
-    <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="B28:AL28"/>
-    <mergeCell ref="B15:AL15"/>
-    <mergeCell ref="D23:R23"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="AF26:AK26"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B11:N11"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="S4:AB6"/>
+    <mergeCell ref="S2:AB3"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B2:N5"/>
+    <mergeCell ref="O2:R3"/>
+    <mergeCell ref="O4:R6"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/invoice_template_direct_v2.xlsx
+++ b/templates/invoice_template_direct_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Проекты\Агент Авто Континент\01_БОТ_АКТУАЛЬНЫЙ\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E8A98C-3E68-476B-9E1A-31A72433F614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8D60C9-7929-41EC-9DC1-3D6B69D7354A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,7 +173,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
@@ -234,6 +234,21 @@
     </font>
     <font>
       <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -600,18 +615,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -625,202 +628,17 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -838,6 +656,203 @@
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -865,10 +880,10 @@
       <xdr:row>32</xdr:row>
       <xdr:rowOff>81493</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1804131" cy="1576024"/>
+    <xdr:ext cx="1768048" cy="1544504"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="image2.png" title="Изображение">
+        <xdr:cNvPr descr="stamp" id="4" name="image2.png" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F869081-3D0B-42FB-8CAB-9AEA07D8FD90}"/>
@@ -885,8 +900,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2631653" y="5627160"/>
-          <a:ext cx="1804131" cy="1576024"/>
+          <a:off x="2631653" y="5961593"/>
+          <a:ext cx="1768048" cy="1544504"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -906,7 +921,7 @@
     <xdr:ext cx="1205130" cy="607695"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="image1.png" title="Изображение">
+        <xdr:cNvPr descr="signature" id="5" name="image1.png" title="Изображение">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C2EBBCE-23F2-4BEB-ABFD-12E548EB3FF5}"/>
@@ -1199,437 +1214,437 @@
       <c r="AK1" s="8"/>
       <c r="AL1" s="8"/>
     </row>
-    <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8"/>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="53"/>
-      <c r="O2" s="57" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="32" t="s">
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
-      <c r="AH2" s="22"/>
-      <c r="AI2" s="22"/>
-      <c r="AJ2" s="22"/>
-      <c r="AK2" s="22"/>
-      <c r="AL2" s="23"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="54"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="55"/>
+      <c r="AG2" s="55"/>
+      <c r="AH2" s="55"/>
+      <c r="AI2" s="55"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="56"/>
     </row>
     <row r="3" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="56"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="59"/>
       <c r="O3" s="60"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="20"/>
-      <c r="AD3" s="47" t="s">
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="62"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="64"/>
+      <c r="V3" s="64"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="64"/>
+      <c r="Y3" s="64"/>
+      <c r="Z3" s="64"/>
+      <c r="AA3" s="64"/>
+      <c r="AB3" s="65"/>
+      <c r="AC3" s="66"/>
+      <c r="AD3" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="AE3" s="47"/>
-      <c r="AF3" s="47"/>
-      <c r="AG3" s="47"/>
-      <c r="AH3" s="47"/>
-      <c r="AI3" s="47"/>
-      <c r="AJ3" s="47"/>
-      <c r="AK3" s="20"/>
-      <c r="AL3" s="21"/>
+      <c r="AE3" s="67"/>
+      <c r="AF3" s="67"/>
+      <c r="AG3" s="67"/>
+      <c r="AH3" s="67"/>
+      <c r="AI3" s="67"/>
+      <c r="AJ3" s="67"/>
+      <c r="AK3" s="66"/>
+      <c r="AL3" s="68"/>
     </row>
     <row r="4" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="59"/>
       <c r="O4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="26" t="s">
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="62"/>
+      <c r="S4" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="47"/>
-      <c r="AE4" s="47"/>
-      <c r="AF4" s="47"/>
-      <c r="AG4" s="47"/>
-      <c r="AH4" s="47"/>
-      <c r="AI4" s="47"/>
-      <c r="AJ4" s="47"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="10"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="65"/>
+      <c r="AC4" s="69"/>
+      <c r="AD4" s="67"/>
+      <c r="AE4" s="67"/>
+      <c r="AF4" s="67"/>
+      <c r="AG4" s="67"/>
+      <c r="AH4" s="67"/>
+      <c r="AI4" s="67"/>
+      <c r="AJ4" s="67"/>
+      <c r="AK4" s="69"/>
+      <c r="AL4" s="70"/>
     </row>
     <row r="5" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="56"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="59"/>
       <c r="O5" s="60"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="12"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="12"/>
-      <c r="AL5" s="13"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="64"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="W5" s="64"/>
+      <c r="X5" s="64"/>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="64"/>
+      <c r="AA5" s="64"/>
+      <c r="AB5" s="65"/>
+      <c r="AC5" s="71"/>
+      <c r="AD5" s="67"/>
+      <c r="AE5" s="67"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="67"/>
+      <c r="AH5" s="67"/>
+      <c r="AI5" s="67"/>
+      <c r="AJ5" s="67"/>
+      <c r="AK5" s="71"/>
+      <c r="AL5" s="72"/>
     </row>
     <row r="6" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="61"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="30"/>
-      <c r="U6" s="30"/>
-      <c r="V6" s="30"/>
-      <c r="W6" s="30"/>
-      <c r="X6" s="30"/>
-      <c r="Y6" s="30"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="12"/>
-      <c r="AD6" s="47"/>
-      <c r="AE6" s="47"/>
-      <c r="AF6" s="47"/>
-      <c r="AG6" s="47"/>
-      <c r="AH6" s="47"/>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="47"/>
-      <c r="AK6" s="12"/>
-      <c r="AL6" s="14"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="74"/>
+      <c r="K6" s="74"/>
+      <c r="L6" s="74"/>
+      <c r="M6" s="74"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="77"/>
+      <c r="Q6" s="77"/>
+      <c r="R6" s="78"/>
+      <c r="S6" s="79"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
+      <c r="Y6" s="80"/>
+      <c r="Z6" s="80"/>
+      <c r="AA6" s="80"/>
+      <c r="AB6" s="81"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="67"/>
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="67"/>
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="67"/>
+      <c r="AJ6" s="67"/>
+      <c r="AK6" s="71"/>
+      <c r="AL6" s="82"/>
     </row>
     <row r="7" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="47" t="s">
+      <c r="C7" s="84"/>
+      <c r="D7" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="80" t="s">
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="85" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="80"/>
-      <c r="K7" s="90" t="s">
+      <c r="J7" s="85"/>
+      <c r="K7" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="90"/>
-      <c r="M7" s="90"/>
-      <c r="N7" s="91"/>
-      <c r="O7" s="43" t="s">
+      <c r="L7" s="86"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="44"/>
-      <c r="S7" s="27" t="s">
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="47"/>
-      <c r="AE7" s="47"/>
-      <c r="AF7" s="47"/>
-      <c r="AG7" s="47"/>
-      <c r="AH7" s="47"/>
-      <c r="AI7" s="47"/>
-      <c r="AJ7" s="47"/>
-      <c r="AK7" s="12"/>
-      <c r="AL7" s="14"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="64"/>
+      <c r="V7" s="64"/>
+      <c r="W7" s="64"/>
+      <c r="X7" s="64"/>
+      <c r="Y7" s="64"/>
+      <c r="Z7" s="64"/>
+      <c r="AA7" s="64"/>
+      <c r="AB7" s="65"/>
+      <c r="AC7" s="88"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="71"/>
+      <c r="AL7" s="82"/>
     </row>
     <row r="8" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="44"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
-      <c r="AA8" s="27"/>
-      <c r="AB8" s="28"/>
-      <c r="AC8" s="11"/>
-      <c r="AD8" s="47"/>
-      <c r="AE8" s="47"/>
-      <c r="AF8" s="47"/>
-      <c r="AG8" s="47"/>
-      <c r="AH8" s="47"/>
-      <c r="AI8" s="47"/>
-      <c r="AJ8" s="47"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="14"/>
+      <c r="C8" s="90"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="90"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="61"/>
+      <c r="P8" s="61"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="64"/>
+      <c r="V8" s="64"/>
+      <c r="W8" s="64"/>
+      <c r="X8" s="64"/>
+      <c r="Y8" s="64"/>
+      <c r="Z8" s="64"/>
+      <c r="AA8" s="64"/>
+      <c r="AB8" s="65"/>
+      <c r="AC8" s="88"/>
+      <c r="AD8" s="67"/>
+      <c r="AE8" s="67"/>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="67"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="67"/>
+      <c r="AJ8" s="67"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="82"/>
     </row>
     <row r="9" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="38"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="44"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="28"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="47"/>
-      <c r="AE9" s="47"/>
-      <c r="AF9" s="47"/>
-      <c r="AG9" s="47"/>
-      <c r="AH9" s="47"/>
-      <c r="AI9" s="47"/>
-      <c r="AJ9" s="47"/>
-      <c r="AK9" s="12"/>
-      <c r="AL9" s="14"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
+      <c r="N9" s="91"/>
+      <c r="O9" s="61"/>
+      <c r="P9" s="61"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="64"/>
+      <c r="T9" s="64"/>
+      <c r="U9" s="64"/>
+      <c r="V9" s="64"/>
+      <c r="W9" s="64"/>
+      <c r="X9" s="64"/>
+      <c r="Y9" s="64"/>
+      <c r="Z9" s="64"/>
+      <c r="AA9" s="64"/>
+      <c r="AB9" s="65"/>
+      <c r="AC9" s="88"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="67"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
+      <c r="AK9" s="71"/>
+      <c r="AL9" s="82"/>
     </row>
     <row r="10" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
-      <c r="AA10" s="27"/>
-      <c r="AB10" s="28"/>
-      <c r="AC10" s="11"/>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="47"/>
-      <c r="AF10" s="47"/>
-      <c r="AG10" s="47"/>
-      <c r="AH10" s="47"/>
-      <c r="AI10" s="47"/>
-      <c r="AJ10" s="47"/>
-      <c r="AK10" s="12"/>
-      <c r="AL10" s="14"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="90"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
+      <c r="L10" s="90"/>
+      <c r="M10" s="90"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="61"/>
+      <c r="P10" s="61"/>
+      <c r="Q10" s="61"/>
+      <c r="R10" s="62"/>
+      <c r="S10" s="64"/>
+      <c r="T10" s="64"/>
+      <c r="U10" s="64"/>
+      <c r="V10" s="64"/>
+      <c r="W10" s="64"/>
+      <c r="X10" s="64"/>
+      <c r="Y10" s="64"/>
+      <c r="Z10" s="64"/>
+      <c r="AA10" s="64"/>
+      <c r="AB10" s="65"/>
+      <c r="AC10" s="88"/>
+      <c r="AD10" s="67"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="67"/>
+      <c r="AG10" s="67"/>
+      <c r="AH10" s="67"/>
+      <c r="AI10" s="67"/>
+      <c r="AJ10" s="67"/>
+      <c r="AK10" s="71"/>
+      <c r="AL10" s="82"/>
     </row>
     <row r="11" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="88"/>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="88"/>
-      <c r="J11" s="88"/>
-      <c r="K11" s="88"/>
-      <c r="L11" s="88"/>
-      <c r="M11" s="88"/>
-      <c r="N11" s="89"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="46"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-      <c r="AA11" s="30"/>
-      <c r="AB11" s="31"/>
-      <c r="AC11" s="40" t="s">
+      <c r="C11" s="93"/>
+      <c r="D11" s="93"/>
+      <c r="E11" s="93"/>
+      <c r="F11" s="93"/>
+      <c r="G11" s="93"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93"/>
+      <c r="J11" s="93"/>
+      <c r="K11" s="93"/>
+      <c r="L11" s="93"/>
+      <c r="M11" s="93"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="77"/>
+      <c r="P11" s="77"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="80"/>
+      <c r="T11" s="80"/>
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="80"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="81"/>
+      <c r="AC11" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="AD11" s="41"/>
-      <c r="AE11" s="41"/>
-      <c r="AF11" s="41"/>
-      <c r="AG11" s="41"/>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="41"/>
-      <c r="AJ11" s="41"/>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="42"/>
+      <c r="AD11" s="96"/>
+      <c r="AE11" s="96"/>
+      <c r="AF11" s="96"/>
+      <c r="AG11" s="96"/>
+      <c r="AH11" s="96"/>
+      <c r="AI11" s="96"/>
+      <c r="AJ11" s="96"/>
+      <c r="AK11" s="96"/>
+      <c r="AL11" s="97"/>
     </row>
     <row r="12" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -1673,125 +1688,125 @@
     </row>
     <row r="13" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="65"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="65"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="65"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="65"/>
-      <c r="M13" s="65"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="65"/>
-      <c r="P13" s="65"/>
-      <c r="Q13" s="65"/>
-      <c r="R13" s="65"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="65"/>
-      <c r="U13" s="65"/>
-      <c r="V13" s="65"/>
-      <c r="W13" s="65"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="65"/>
-      <c r="Z13" s="65"/>
-      <c r="AA13" s="65"/>
-      <c r="AB13" s="65"/>
-      <c r="AC13" s="65"/>
-      <c r="AD13" s="65"/>
-      <c r="AE13" s="65"/>
-      <c r="AF13" s="65"/>
-      <c r="AG13" s="65"/>
-      <c r="AH13" s="65"/>
-      <c r="AI13" s="65"/>
-      <c r="AJ13" s="65"/>
-      <c r="AK13" s="65"/>
-      <c r="AL13" s="65"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="40"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="40"/>
+      <c r="T13" s="40"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="40"/>
+      <c r="W13" s="40"/>
+      <c r="X13" s="40"/>
+      <c r="Y13" s="40"/>
+      <c r="Z13" s="40"/>
+      <c r="AA13" s="40"/>
+      <c r="AB13" s="40"/>
+      <c r="AC13" s="40"/>
+      <c r="AD13" s="40"/>
+      <c r="AE13" s="40"/>
+      <c r="AF13" s="40"/>
+      <c r="AG13" s="40"/>
+      <c r="AH13" s="40"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
     </row>
     <row r="14" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="65"/>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="65"/>
-      <c r="AB14" s="65"/>
-      <c r="AC14" s="65"/>
-      <c r="AD14" s="65"/>
-      <c r="AE14" s="65"/>
-      <c r="AF14" s="65"/>
-      <c r="AG14" s="65"/>
-      <c r="AH14" s="65"/>
-      <c r="AI14" s="65"/>
-      <c r="AJ14" s="65"/>
-      <c r="AK14" s="65"/>
-      <c r="AL14" s="65"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+      <c r="R14" s="40"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="40"/>
+      <c r="U14" s="40"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="40"/>
+      <c r="X14" s="40"/>
+      <c r="Y14" s="40"/>
+      <c r="Z14" s="40"/>
+      <c r="AA14" s="40"/>
+      <c r="AB14" s="40"/>
+      <c r="AC14" s="40"/>
+      <c r="AD14" s="40"/>
+      <c r="AE14" s="40"/>
+      <c r="AF14" s="40"/>
+      <c r="AG14" s="40"/>
+      <c r="AH14" s="40"/>
+      <c r="AI14" s="40"/>
+      <c r="AJ14" s="40"/>
+      <c r="AK14" s="40"/>
+      <c r="AL14" s="40"/>
     </row>
     <row r="15" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="84"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="H15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="84"/>
-      <c r="O15" s="84"/>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="84"/>
-      <c r="AE15" s="84"/>
-      <c r="AF15" s="84"/>
-      <c r="AG15" s="84"/>
-      <c r="AH15" s="84"/>
-      <c r="AI15" s="84"/>
-      <c r="AJ15" s="84"/>
-      <c r="AK15" s="84"/>
-      <c r="AL15" s="84"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="34"/>
+      <c r="X15" s="34"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15" s="34"/>
+      <c r="AA15" s="34"/>
+      <c r="AB15" s="34"/>
+      <c r="AC15" s="34"/>
+      <c r="AD15" s="34"/>
+      <c r="AE15" s="34"/>
+      <c r="AF15" s="34"/>
+      <c r="AG15" s="34"/>
+      <c r="AH15" s="34"/>
+      <c r="AI15" s="34"/>
+      <c r="AJ15" s="34"/>
+      <c r="AK15" s="34"/>
+      <c r="AL15" s="34"/>
     </row>
     <row r="16" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -1835,47 +1850,47 @@
     </row>
     <row r="17" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="68" t="s">
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="68"/>
-      <c r="P17" s="68"/>
-      <c r="Q17" s="68"/>
-      <c r="R17" s="68"/>
-      <c r="S17" s="68"/>
-      <c r="T17" s="68"/>
-      <c r="U17" s="68"/>
-      <c r="V17" s="68"/>
-      <c r="W17" s="68"/>
-      <c r="X17" s="68"/>
-      <c r="Y17" s="68"/>
-      <c r="Z17" s="68"/>
-      <c r="AA17" s="68"/>
-      <c r="AB17" s="68"/>
-      <c r="AC17" s="68"/>
-      <c r="AD17" s="68"/>
-      <c r="AE17" s="68"/>
-      <c r="AF17" s="68"/>
-      <c r="AG17" s="68"/>
-      <c r="AH17" s="68"/>
-      <c r="AI17" s="68"/>
-      <c r="AJ17" s="68"/>
-      <c r="AK17" s="68"/>
-      <c r="AL17" s="68"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="42"/>
+      <c r="V17" s="42"/>
+      <c r="W17" s="42"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="42"/>
+      <c r="AH17" s="42"/>
+      <c r="AI17" s="42"/>
+      <c r="AJ17" s="42"/>
+      <c r="AK17" s="42"/>
+      <c r="AL17" s="42"/>
     </row>
     <row r="18" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1919,47 +1934,47 @@
     </row>
     <row r="19" spans="1:38" ht="26.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="68" t="s">
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="68"/>
-      <c r="P19" s="68"/>
-      <c r="Q19" s="68"/>
-      <c r="R19" s="68"/>
-      <c r="S19" s="68"/>
-      <c r="T19" s="68"/>
-      <c r="U19" s="68"/>
-      <c r="V19" s="68"/>
-      <c r="W19" s="68"/>
-      <c r="X19" s="68"/>
-      <c r="Y19" s="68"/>
-      <c r="Z19" s="68"/>
-      <c r="AA19" s="68"/>
-      <c r="AB19" s="68"/>
-      <c r="AC19" s="68"/>
-      <c r="AD19" s="68"/>
-      <c r="AE19" s="68"/>
-      <c r="AF19" s="68"/>
-      <c r="AG19" s="68"/>
-      <c r="AH19" s="68"/>
-      <c r="AI19" s="68"/>
-      <c r="AJ19" s="68"/>
-      <c r="AK19" s="68"/>
-      <c r="AL19" s="68"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="42"/>
+      <c r="V19" s="42"/>
+      <c r="W19" s="42"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="42"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="42"/>
+      <c r="AC19" s="42"/>
+      <c r="AD19" s="42"/>
+      <c r="AE19" s="42"/>
+      <c r="AF19" s="42"/>
+      <c r="AG19" s="42"/>
+      <c r="AH19" s="42"/>
+      <c r="AI19" s="42"/>
+      <c r="AJ19" s="42"/>
+      <c r="AK19" s="42"/>
+      <c r="AL19" s="42"/>
     </row>
     <row r="20" spans="1:38" ht="6.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2003,160 +2018,160 @@
     </row>
     <row r="21" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="86" t="s">
+      <c r="B21" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="78"/>
-      <c r="D21" s="77" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="78"/>
-      <c r="M21" s="78"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="77" t="s">
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18"/>
+      <c r="R21" s="18"/>
+      <c r="S21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="77" t="s">
+      <c r="T21" s="18"/>
+      <c r="U21" s="18"/>
+      <c r="V21" s="18"/>
+      <c r="W21" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="X21" s="78"/>
-      <c r="Y21" s="78"/>
-      <c r="Z21" s="92" t="s">
+      <c r="X21" s="18"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="AA21" s="93"/>
-      <c r="AB21" s="93"/>
-      <c r="AC21" s="93"/>
-      <c r="AD21" s="93"/>
-      <c r="AE21" s="94"/>
-      <c r="AF21" s="81" t="s">
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="21"/>
+      <c r="AF21" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="AG21" s="78"/>
-      <c r="AH21" s="78"/>
-      <c r="AI21" s="78"/>
-      <c r="AJ21" s="78"/>
-      <c r="AK21" s="82"/>
+      <c r="AG21" s="18"/>
+      <c r="AH21" s="18"/>
+      <c r="AI21" s="18"/>
+      <c r="AJ21" s="18"/>
+      <c r="AK21" s="32"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" ht="52.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
-      <c r="B22" s="63">
+      <c r="B22" s="14">
         <v>1</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="73" t="s">
+      <c r="C22" s="15"/>
+      <c r="D22" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="64"/>
-      <c r="F22" s="64"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64"/>
-      <c r="R22" s="64"/>
-      <c r="S22" s="79">
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="28">
         <v>1</v>
       </c>
-      <c r="T22" s="64"/>
-      <c r="U22" s="64"/>
-      <c r="V22" s="64"/>
-      <c r="W22" s="85" t="s">
+      <c r="T22" s="15"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X22" s="64"/>
-      <c r="Y22" s="64"/>
-      <c r="Z22" s="95" t="s">
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="AA22" s="96"/>
-      <c r="AB22" s="96"/>
-      <c r="AC22" s="96"/>
-      <c r="AD22" s="96"/>
-      <c r="AE22" s="97"/>
-      <c r="AF22" s="66" t="e">
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="23"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="29" t="e">
         <f>S22*Z22</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="67"/>
+      <c r="AG22" s="15"/>
+      <c r="AH22" s="15"/>
+      <c r="AI22" s="15"/>
+      <c r="AJ22" s="15"/>
+      <c r="AK22" s="30"/>
       <c r="AL22" s="3"/>
     </row>
     <row r="23" spans="1:38" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
-      <c r="B23" s="63">
+      <c r="B23" s="14">
         <v>2</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="73" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="64"/>
-      <c r="F23" s="64"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
-      <c r="K23" s="64"/>
-      <c r="L23" s="64"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="64"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="64"/>
-      <c r="R23" s="64"/>
-      <c r="S23" s="79">
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="28">
         <v>1</v>
       </c>
-      <c r="T23" s="64"/>
-      <c r="U23" s="64"/>
-      <c r="V23" s="64"/>
-      <c r="W23" s="85" t="s">
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="X23" s="64"/>
-      <c r="Y23" s="64"/>
-      <c r="Z23" s="74" t="s">
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="AA23" s="75"/>
-      <c r="AB23" s="75"/>
-      <c r="AC23" s="75"/>
-      <c r="AD23" s="75"/>
-      <c r="AE23" s="76"/>
-      <c r="AF23" s="66" t="e">
+      <c r="AA23" s="44"/>
+      <c r="AB23" s="44"/>
+      <c r="AC23" s="44"/>
+      <c r="AD23" s="44"/>
+      <c r="AE23" s="45"/>
+      <c r="AF23" s="29" t="e">
         <f>S23*Z23</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG23" s="64"/>
-      <c r="AH23" s="64"/>
-      <c r="AI23" s="64"/>
-      <c r="AJ23" s="64"/>
-      <c r="AK23" s="67"/>
+      <c r="AG23" s="15"/>
+      <c r="AH23" s="15"/>
+      <c r="AI23" s="15"/>
+      <c r="AJ23" s="15"/>
+      <c r="AK23" s="30"/>
       <c r="AL23" s="3"/>
     </row>
     <row r="24" spans="1:38" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2229,19 +2244,19 @@
       <c r="AA25" s="5"/>
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15" t="s">
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AF25" s="72" t="e">
+      <c r="AF25" s="37" t="e">
         <f>SUM(AF22:AK23)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG25" s="36"/>
-      <c r="AH25" s="36"/>
-      <c r="AI25" s="36"/>
-      <c r="AJ25" s="36"/>
-      <c r="AK25" s="36"/>
+      <c r="AG25" s="38"/>
+      <c r="AH25" s="38"/>
+      <c r="AI25" s="38"/>
+      <c r="AJ25" s="38"/>
+      <c r="AK25" s="38"/>
       <c r="AL25" s="1"/>
     </row>
     <row r="26" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2274,18 +2289,18 @@
       <c r="AA26" s="5"/>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
-      <c r="AD26" s="15"/>
-      <c r="AE26" s="15" t="s">
+      <c r="AD26" s="9"/>
+      <c r="AE26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AF26" s="72" t="s">
+      <c r="AF26" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="AG26" s="36"/>
-      <c r="AH26" s="36"/>
-      <c r="AI26" s="36"/>
-      <c r="AJ26" s="36"/>
-      <c r="AK26" s="36"/>
+      <c r="AG26" s="38"/>
+      <c r="AH26" s="38"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="38"/>
+      <c r="AK26" s="38"/>
       <c r="AL26" s="1"/>
     </row>
     <row r="27" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -2318,102 +2333,102 @@
       <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
-      <c r="AD27" s="15"/>
-      <c r="AE27" s="15" t="s">
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AF27" s="72" t="e">
+      <c r="AF27" s="37" t="e">
         <f>SUM(AF25:AK26)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG27" s="36"/>
-      <c r="AH27" s="36"/>
-      <c r="AI27" s="36"/>
-      <c r="AJ27" s="36"/>
-      <c r="AK27" s="36"/>
+      <c r="AG27" s="38"/>
+      <c r="AH27" s="38"/>
+      <c r="AI27" s="38"/>
+      <c r="AJ27" s="38"/>
+      <c r="AK27" s="38"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-      <c r="R28" s="83"/>
-      <c r="S28" s="83"/>
-      <c r="T28" s="83"/>
-      <c r="U28" s="83"/>
-      <c r="V28" s="83"/>
-      <c r="W28" s="83"/>
-      <c r="X28" s="83"/>
-      <c r="Y28" s="83"/>
-      <c r="Z28" s="83"/>
-      <c r="AA28" s="83"/>
-      <c r="AB28" s="83"/>
-      <c r="AC28" s="83"/>
-      <c r="AD28" s="83"/>
-      <c r="AE28" s="83"/>
-      <c r="AF28" s="83"/>
-      <c r="AG28" s="83"/>
-      <c r="AH28" s="83"/>
-      <c r="AI28" s="83"/>
-      <c r="AJ28" s="83"/>
-      <c r="AK28" s="83"/>
-      <c r="AL28" s="83"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="33"/>
+      <c r="AB28" s="33"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="33"/>
+      <c r="AE28" s="33"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="33"/>
+      <c r="AH28" s="33"/>
+      <c r="AI28" s="33"/>
+      <c r="AJ28" s="33"/>
+      <c r="AK28" s="33"/>
+      <c r="AL28" s="33"/>
     </row>
     <row r="29" spans="1:38" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
-      <c r="B29" s="68" t="s">
+      <c r="B29" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
-      <c r="R29" s="68"/>
-      <c r="S29" s="68"/>
-      <c r="T29" s="68"/>
-      <c r="U29" s="68"/>
-      <c r="V29" s="68"/>
-      <c r="W29" s="68"/>
-      <c r="X29" s="68"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="68"/>
-      <c r="AA29" s="68"/>
-      <c r="AB29" s="68"/>
-      <c r="AC29" s="68"/>
-      <c r="AD29" s="68"/>
-      <c r="AE29" s="68"/>
-      <c r="AF29" s="68"/>
-      <c r="AG29" s="68"/>
-      <c r="AH29" s="68"/>
-      <c r="AI29" s="68"/>
-      <c r="AJ29" s="68"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41"/>
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="41"/>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3"/>
     </row>
@@ -2537,219 +2552,219 @@
       <c r="AK32" s="1"/>
       <c r="AL32" s="1"/>
     </row>
-    <row r="33" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16"/>
-      <c r="B33" s="17" t="s">
+    <row r="33" spans="1:38" s="13" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="18"/>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="62" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="T33" s="62"/>
-      <c r="U33" s="62"/>
-      <c r="V33" s="62"/>
-      <c r="W33" s="62"/>
-      <c r="X33" s="62"/>
-      <c r="Y33" s="62"/>
-      <c r="Z33" s="62"/>
-      <c r="AA33" s="62"/>
-      <c r="AB33" s="62"/>
-      <c r="AC33" s="62"/>
-      <c r="AD33" s="62"/>
-      <c r="AE33" s="62"/>
-      <c r="AF33" s="62"/>
-      <c r="AG33" s="62"/>
-      <c r="AH33" s="16"/>
-      <c r="AI33" s="16"/>
-      <c r="AJ33" s="16"/>
-      <c r="AK33" s="16"/>
-      <c r="AL33" s="16"/>
-    </row>
-    <row r="34" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="70" t="s">
+      <c r="T33" s="39"/>
+      <c r="U33" s="39"/>
+      <c r="V33" s="39"/>
+      <c r="W33" s="39"/>
+      <c r="X33" s="39"/>
+      <c r="Y33" s="39"/>
+      <c r="Z33" s="39"/>
+      <c r="AA33" s="39"/>
+      <c r="AB33" s="39"/>
+      <c r="AC33" s="39"/>
+      <c r="AD33" s="39"/>
+      <c r="AE33" s="39"/>
+      <c r="AF33" s="39"/>
+      <c r="AG33" s="39"/>
+      <c r="AH33" s="10"/>
+      <c r="AI33" s="10"/>
+      <c r="AJ33" s="10"/>
+      <c r="AK33" s="10"/>
+      <c r="AL33" s="10"/>
+    </row>
+    <row r="34" spans="1:38" s="13" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="69" t="s">
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="T34" s="69"/>
-      <c r="U34" s="69"/>
-      <c r="V34" s="69"/>
-      <c r="W34" s="69"/>
-      <c r="X34" s="69"/>
-      <c r="Y34" s="69"/>
-      <c r="Z34" s="69"/>
-      <c r="AA34" s="69"/>
-      <c r="AB34" s="69"/>
-      <c r="AC34" s="69"/>
-      <c r="AD34" s="69"/>
-      <c r="AE34" s="69"/>
-      <c r="AF34" s="69"/>
-      <c r="AG34" s="69"/>
-      <c r="AH34" s="16"/>
-      <c r="AI34" s="16"/>
-      <c r="AJ34" s="16"/>
-      <c r="AK34" s="16"/>
-      <c r="AL34" s="16"/>
-    </row>
-    <row r="35" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
-      <c r="AA35" s="16"/>
-      <c r="AB35" s="16"/>
-      <c r="AC35" s="16"/>
-      <c r="AD35" s="16"/>
-      <c r="AE35" s="16"/>
-      <c r="AF35" s="16"/>
-      <c r="AG35" s="16"/>
-      <c r="AH35" s="16"/>
-      <c r="AI35" s="16"/>
-      <c r="AJ35" s="16"/>
-      <c r="AK35" s="16"/>
-      <c r="AL35" s="16"/>
-    </row>
-    <row r="36" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="16"/>
-      <c r="B36" s="17" t="s">
+      <c r="T34" s="27"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="27"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="27"/>
+      <c r="AA34" s="27"/>
+      <c r="AB34" s="27"/>
+      <c r="AC34" s="27"/>
+      <c r="AD34" s="27"/>
+      <c r="AE34" s="27"/>
+      <c r="AF34" s="27"/>
+      <c r="AG34" s="27"/>
+      <c r="AH34" s="10"/>
+      <c r="AI34" s="10"/>
+      <c r="AJ34" s="10"/>
+      <c r="AK34" s="10"/>
+      <c r="AL34" s="10"/>
+    </row>
+    <row r="35" spans="1:38" s="13" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
+      <c r="AA35" s="10"/>
+      <c r="AB35" s="10"/>
+      <c r="AC35" s="10"/>
+      <c r="AD35" s="10"/>
+      <c r="AE35" s="10"/>
+      <c r="AF35" s="10"/>
+      <c r="AG35" s="10"/>
+      <c r="AH35" s="10"/>
+      <c r="AI35" s="10"/>
+      <c r="AJ35" s="10"/>
+      <c r="AK35" s="10"/>
+      <c r="AL35" s="10"/>
+    </row>
+    <row r="36" spans="1:38" s="13" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="18"/>
-      <c r="L36" s="18"/>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="O36" s="18"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="18"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="62"/>
-      <c r="T36" s="62"/>
-      <c r="U36" s="62"/>
-      <c r="V36" s="62"/>
-      <c r="W36" s="62"/>
-      <c r="X36" s="62"/>
-      <c r="Y36" s="62"/>
-      <c r="Z36" s="62"/>
-      <c r="AA36" s="62"/>
-      <c r="AB36" s="62"/>
-      <c r="AC36" s="62"/>
-      <c r="AD36" s="62"/>
-      <c r="AE36" s="62"/>
-      <c r="AF36" s="62"/>
-      <c r="AG36" s="62"/>
-      <c r="AH36" s="16"/>
-      <c r="AI36" s="16"/>
-      <c r="AJ36" s="16"/>
-      <c r="AK36" s="16"/>
-      <c r="AL36" s="16"/>
-    </row>
-    <row r="37" spans="1:38" s="19" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-      <c r="J37" s="70" t="s">
+      <c r="C36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="39"/>
+      <c r="T36" s="39"/>
+      <c r="U36" s="39"/>
+      <c r="V36" s="39"/>
+      <c r="W36" s="39"/>
+      <c r="X36" s="39"/>
+      <c r="Y36" s="39"/>
+      <c r="Z36" s="39"/>
+      <c r="AA36" s="39"/>
+      <c r="AB36" s="39"/>
+      <c r="AC36" s="39"/>
+      <c r="AD36" s="39"/>
+      <c r="AE36" s="39"/>
+      <c r="AF36" s="39"/>
+      <c r="AG36" s="39"/>
+      <c r="AH36" s="10"/>
+      <c r="AI36" s="10"/>
+      <c r="AJ36" s="10"/>
+      <c r="AK36" s="10"/>
+      <c r="AL36" s="10"/>
+    </row>
+    <row r="37" spans="1:38" s="13" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="K37" s="71"/>
-      <c r="L37" s="71"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="71"/>
-      <c r="O37" s="71"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="71"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="69" t="s">
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="69"/>
-      <c r="U37" s="69"/>
-      <c r="V37" s="69"/>
-      <c r="W37" s="69"/>
-      <c r="X37" s="69"/>
-      <c r="Y37" s="69"/>
-      <c r="Z37" s="69"/>
-      <c r="AA37" s="69"/>
-      <c r="AB37" s="69"/>
-      <c r="AC37" s="69"/>
-      <c r="AD37" s="69"/>
-      <c r="AE37" s="69"/>
-      <c r="AF37" s="69"/>
-      <c r="AG37" s="69"/>
-      <c r="AH37" s="16"/>
-      <c r="AI37" s="16"/>
-      <c r="AJ37" s="16"/>
-      <c r="AK37" s="16"/>
-      <c r="AL37" s="16"/>
+      <c r="T37" s="27"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="27"/>
+      <c r="W37" s="27"/>
+      <c r="X37" s="27"/>
+      <c r="Y37" s="27"/>
+      <c r="Z37" s="27"/>
+      <c r="AA37" s="27"/>
+      <c r="AB37" s="27"/>
+      <c r="AC37" s="27"/>
+      <c r="AD37" s="27"/>
+      <c r="AE37" s="27"/>
+      <c r="AF37" s="27"/>
+      <c r="AG37" s="27"/>
+      <c r="AH37" s="10"/>
+      <c r="AI37" s="10"/>
+      <c r="AJ37" s="10"/>
+      <c r="AK37" s="10"/>
+      <c r="AL37" s="10"/>
     </row>
     <row r="38" spans="1:38" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
@@ -2768,7 +2783,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="16" t="s">
+      <c r="Q38" s="10" t="s">
         <v>36</v>
       </c>
       <c r="R38" s="1"/>
@@ -41155,12 +41170,34 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="D21:R21"/>
-    <mergeCell ref="Z21:AE21"/>
-    <mergeCell ref="S21:V21"/>
-    <mergeCell ref="Z22:AE22"/>
+    <mergeCell ref="S4:AB6"/>
+    <mergeCell ref="S2:AB3"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B8:N10"/>
+    <mergeCell ref="AC11:AL11"/>
+    <mergeCell ref="O7:R11"/>
+    <mergeCell ref="AD3:AJ10"/>
+    <mergeCell ref="S7:AB11"/>
+    <mergeCell ref="B6:N6"/>
+    <mergeCell ref="B2:N5"/>
+    <mergeCell ref="O2:R3"/>
+    <mergeCell ref="O4:R6"/>
+    <mergeCell ref="S36:AG36"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:AL14"/>
+    <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="B29:AJ29"/>
+    <mergeCell ref="G19:AL19"/>
+    <mergeCell ref="S34:AG34"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="J34:Q34"/>
+    <mergeCell ref="AF27:AK27"/>
+    <mergeCell ref="S33:AG33"/>
+    <mergeCell ref="D22:R22"/>
+    <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Z23:AE23"/>
+    <mergeCell ref="G17:AL17"/>
+    <mergeCell ref="W21:Y21"/>
     <mergeCell ref="J37:Q37"/>
     <mergeCell ref="S37:AG37"/>
     <mergeCell ref="S23:V23"/>
@@ -41177,34 +41214,12 @@
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="B11:N11"/>
     <mergeCell ref="K7:N7"/>
-    <mergeCell ref="S36:AG36"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:AL14"/>
-    <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="B29:AJ29"/>
-    <mergeCell ref="G19:AL19"/>
-    <mergeCell ref="S34:AG34"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="J34:Q34"/>
-    <mergeCell ref="AF27:AK27"/>
-    <mergeCell ref="S33:AG33"/>
-    <mergeCell ref="D22:R22"/>
-    <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="Z23:AE23"/>
-    <mergeCell ref="G17:AL17"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="S4:AB6"/>
-    <mergeCell ref="S2:AB3"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B8:N10"/>
-    <mergeCell ref="AC11:AL11"/>
-    <mergeCell ref="O7:R11"/>
-    <mergeCell ref="AD3:AJ10"/>
-    <mergeCell ref="S7:AB11"/>
-    <mergeCell ref="B6:N6"/>
-    <mergeCell ref="B2:N5"/>
-    <mergeCell ref="O2:R3"/>
-    <mergeCell ref="O4:R6"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="D21:R21"/>
+    <mergeCell ref="Z21:AE21"/>
+    <mergeCell ref="S21:V21"/>
+    <mergeCell ref="Z22:AE22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId1"/>
